--- a/research/traditional_assets/database/data/finland/finland_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_rubber_tires.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08737229804633942</v>
+        <v>0.08723355345024676</v>
       </c>
       <c r="C2">
-        <v>1962.619177850073</v>
+        <v>1947.381148456389</v>
       </c>
       <c r="D2">
-        <v>1783.719177850073</v>
+        <v>1789.692148456389</v>
       </c>
       <c r="E2">
-        <v>-1072.6</v>
+        <v>-1051.389</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21.211</v>
       </c>
       <c r="G2">
         <v>178.9</v>
@@ -1582,28 +1582,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.0669133</v>
       </c>
       <c r="N2">
-        <v>93.13333333333335</v>
+        <v>92.06642003333336</v>
       </c>
       <c r="O2">
-        <v>18.62666666666667</v>
+        <v>18.41328400666667</v>
       </c>
       <c r="P2">
-        <v>74.50666666666669</v>
+        <v>73.65313602666669</v>
       </c>
       <c r="Q2">
-        <v>160.7066666666667</v>
+        <v>159.8531360266667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08737229804633942</v>
+        <v>0.08770823580833007</v>
       </c>
       <c r="T2">
-        <v>0.8547702034345667</v>
+        <v>0.8616774374017148</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>87.29231637972211</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08723355345024676</v>
+        <v>0.08709480885415406</v>
       </c>
       <c r="C3">
-        <v>1947.381148456389</v>
+        <v>1932.183255700567</v>
       </c>
       <c r="D3">
-        <v>1789.692148456389</v>
+        <v>1795.705255700567</v>
       </c>
       <c r="E3">
-        <v>-1051.389</v>
+        <v>-1030.178</v>
       </c>
       <c r="F3">
-        <v>21.211</v>
+        <v>42.422</v>
       </c>
       <c r="G3">
         <v>178.9</v>
@@ -1664,28 +1664,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M3">
-        <v>1.0669133</v>
+        <v>2.1338266</v>
       </c>
       <c r="N3">
-        <v>92.06642003333336</v>
+        <v>90.99950673333335</v>
       </c>
       <c r="O3">
-        <v>18.41328400666667</v>
+        <v>18.19990134666667</v>
       </c>
       <c r="P3">
-        <v>73.65313602666669</v>
+        <v>72.79960538666668</v>
       </c>
       <c r="Q3">
-        <v>159.8531360266667</v>
+        <v>158.9996053866667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08770823580833007</v>
+        <v>0.08805102944301435</v>
       </c>
       <c r="T3">
-        <v>0.8616774374017148</v>
+        <v>0.8687256353273759</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>87.29231637972211</v>
+        <v>43.64615818986105</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08709480885415406</v>
+        <v>0.08695606425806141</v>
       </c>
       <c r="C4">
-        <v>1932.183255700567</v>
+        <v>1917.025905506375</v>
       </c>
       <c r="D4">
-        <v>1795.705255700567</v>
+        <v>1801.758905506375</v>
       </c>
       <c r="E4">
-        <v>-1030.178</v>
+        <v>-1008.967</v>
       </c>
       <c r="F4">
-        <v>42.422</v>
+        <v>63.633</v>
       </c>
       <c r="G4">
         <v>178.9</v>
@@ -1746,28 +1746,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M4">
-        <v>2.1338266</v>
+        <v>3.200739899999999</v>
       </c>
       <c r="N4">
-        <v>90.99950673333335</v>
+        <v>89.93259343333335</v>
       </c>
       <c r="O4">
-        <v>18.19990134666667</v>
+        <v>17.98651868666667</v>
       </c>
       <c r="P4">
-        <v>72.79960538666668</v>
+        <v>71.94607474666668</v>
       </c>
       <c r="Q4">
-        <v>158.9996053866667</v>
+        <v>158.1460747466667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08805102944301435</v>
+        <v>0.08840089098769216</v>
       </c>
       <c r="T4">
-        <v>0.8687256353273759</v>
+        <v>0.8759191569216074</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>43.64615818986105</v>
+        <v>29.0974387932407</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08695606425806141</v>
+        <v>0.08681731966196872</v>
       </c>
       <c r="C5">
-        <v>1917.025905506375</v>
+        <v>1901.909509289876</v>
       </c>
       <c r="D5">
-        <v>1801.758905506375</v>
+        <v>1807.853509289876</v>
       </c>
       <c r="E5">
-        <v>-1008.967</v>
+        <v>-987.7559999999999</v>
       </c>
       <c r="F5">
-        <v>63.633</v>
+        <v>84.84399999999999</v>
       </c>
       <c r="G5">
         <v>178.9</v>
@@ -1828,28 +1828,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M5">
-        <v>3.200739899999999</v>
+        <v>4.2676532</v>
       </c>
       <c r="N5">
-        <v>89.93259343333335</v>
+        <v>88.86568013333336</v>
       </c>
       <c r="O5">
-        <v>17.98651868666667</v>
+        <v>17.77313602666667</v>
       </c>
       <c r="P5">
-        <v>71.94607474666668</v>
+        <v>71.09254410666668</v>
       </c>
       <c r="Q5">
-        <v>158.1460747466667</v>
+        <v>157.2925441066667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08840089098769216</v>
+        <v>0.08875804131455076</v>
       </c>
       <c r="T5">
-        <v>0.8759191569216074</v>
+        <v>0.8832625435490523</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>29.0974387932407</v>
+        <v>21.82307909493052</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08681731966196872</v>
+        <v>0.08667857506587603</v>
       </c>
       <c r="C6">
-        <v>1901.909509289876</v>
+        <v>1886.83448405262</v>
       </c>
       <c r="D6">
-        <v>1807.853509289876</v>
+        <v>1813.98948405262</v>
       </c>
       <c r="E6">
-        <v>-987.7559999999999</v>
+        <v>-966.5449999999998</v>
       </c>
       <c r="F6">
-        <v>84.84399999999999</v>
+        <v>106.055</v>
       </c>
       <c r="G6">
         <v>178.9</v>
@@ -1910,28 +1910,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M6">
-        <v>4.2676532</v>
+        <v>5.3345665</v>
       </c>
       <c r="N6">
-        <v>88.86568013333336</v>
+        <v>87.79876683333336</v>
       </c>
       <c r="O6">
-        <v>17.77313602666667</v>
+        <v>17.55975336666667</v>
       </c>
       <c r="P6">
-        <v>71.09254410666668</v>
+        <v>70.23901346666669</v>
       </c>
       <c r="Q6">
-        <v>157.2925441066667</v>
+        <v>156.4390134666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08875804131455076</v>
+        <v>0.08912271059565899</v>
       </c>
       <c r="T6">
-        <v>0.8832625435490523</v>
+        <v>0.8907605277897063</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.82307909493052</v>
+        <v>17.45846327594442</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08667857506587603</v>
+        <v>0.08653983046978335</v>
       </c>
       <c r="C7">
-        <v>1886.83448405262</v>
+        <v>1871.801252476765</v>
       </c>
       <c r="D7">
-        <v>1813.98948405262</v>
+        <v>1820.167252476765</v>
       </c>
       <c r="E7">
-        <v>-966.5449999999998</v>
+        <v>-945.3339999999999</v>
       </c>
       <c r="F7">
-        <v>106.055</v>
+        <v>127.266</v>
       </c>
       <c r="G7">
         <v>178.9</v>
@@ -1992,28 +1992,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M7">
-        <v>5.3345665</v>
+        <v>6.4014798</v>
       </c>
       <c r="N7">
-        <v>87.79876683333336</v>
+        <v>86.73185353333335</v>
       </c>
       <c r="O7">
-        <v>17.55975336666667</v>
+        <v>17.34637070666667</v>
       </c>
       <c r="P7">
-        <v>70.23901346666669</v>
+        <v>69.38548282666667</v>
       </c>
       <c r="Q7">
-        <v>156.4390134666667</v>
+        <v>155.5854828266667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08912271059565899</v>
+        <v>0.08949513879764187</v>
       </c>
       <c r="T7">
-        <v>0.8907605277897063</v>
+        <v>0.8984180436099488</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.45846327594442</v>
+        <v>14.54871939662035</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08653983046978335</v>
+        <v>0.08648508587369068</v>
       </c>
       <c r="C8">
-        <v>1871.801252476765</v>
+        <v>1853.03941336504</v>
       </c>
       <c r="D8">
-        <v>1820.167252476765</v>
+        <v>1822.61641336504</v>
       </c>
       <c r="E8">
-        <v>-945.3339999999999</v>
+        <v>-924.1229999999999</v>
       </c>
       <c r="F8">
-        <v>127.266</v>
+        <v>148.477</v>
       </c>
       <c r="G8">
         <v>178.9</v>
@@ -2074,45 +2074,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M8">
-        <v>6.401479799999999</v>
+        <v>7.691108599999999</v>
       </c>
       <c r="N8">
-        <v>86.73185353333335</v>
+        <v>85.44222473333336</v>
       </c>
       <c r="O8">
-        <v>17.34637070666667</v>
+        <v>17.08844494666667</v>
       </c>
       <c r="P8">
-        <v>69.38548282666667</v>
+        <v>68.35377978666669</v>
       </c>
       <c r="Q8">
-        <v>155.5854828266667</v>
+        <v>154.5537797866667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08949513879764187</v>
+        <v>0.08987557620826955</v>
       </c>
       <c r="T8">
-        <v>0.8984180436099488</v>
+        <v>0.9062402371897664</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.54871939662035</v>
+        <v>12.10922094291236</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08648508587369068</v>
+        <v>0.08635834127759801</v>
       </c>
       <c r="C9">
-        <v>1853.03941336504</v>
+        <v>1837.524079752448</v>
       </c>
       <c r="D9">
-        <v>1822.61641336504</v>
+        <v>1828.312079752448</v>
       </c>
       <c r="E9">
-        <v>-924.1229999999999</v>
+        <v>-902.9119999999999</v>
       </c>
       <c r="F9">
-        <v>148.477</v>
+        <v>169.688</v>
       </c>
       <c r="G9">
         <v>178.9</v>
@@ -2156,28 +2156,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M9">
-        <v>7.6911086</v>
+        <v>8.789838399999999</v>
       </c>
       <c r="N9">
-        <v>85.44222473333335</v>
+        <v>84.34349493333336</v>
       </c>
       <c r="O9">
-        <v>17.08844494666667</v>
+        <v>16.86869898666667</v>
       </c>
       <c r="P9">
-        <v>68.35377978666668</v>
+        <v>67.47479594666669</v>
       </c>
       <c r="Q9">
-        <v>154.5537797866667</v>
+        <v>153.6747959466667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08987557620826955</v>
+        <v>0.09026428399738913</v>
       </c>
       <c r="T9">
-        <v>0.9062402371897664</v>
+        <v>0.9142324784561018</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>12.10922094291236</v>
+        <v>10.59556832504832</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08635834127759801</v>
+        <v>0.08635399668150533</v>
       </c>
       <c r="C10">
-        <v>1837.524079752448</v>
+        <v>1816.508948918692</v>
       </c>
       <c r="D10">
-        <v>1828.312079752448</v>
+        <v>1828.507948918692</v>
       </c>
       <c r="E10">
-        <v>-902.9119999999999</v>
+        <v>-881.7009999999999</v>
       </c>
       <c r="F10">
-        <v>169.688</v>
+        <v>190.899</v>
       </c>
       <c r="G10">
         <v>178.9</v>
@@ -2238,45 +2238,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M10">
-        <v>8.789838399999999</v>
+        <v>10.2130965</v>
       </c>
       <c r="N10">
-        <v>84.34349493333336</v>
+        <v>82.92023683333335</v>
       </c>
       <c r="O10">
-        <v>16.86869898666667</v>
+        <v>16.58404736666667</v>
       </c>
       <c r="P10">
-        <v>67.47479594666669</v>
+        <v>66.33618946666668</v>
       </c>
       <c r="Q10">
-        <v>153.6747959466667</v>
+        <v>152.5361894666667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09026428399738913</v>
+        <v>0.09066153481484102</v>
       </c>
       <c r="T10">
-        <v>0.9142324784561018</v>
+        <v>0.9224003733766423</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.59556832504832</v>
+        <v>9.119010413084156</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08635399668150533</v>
+        <v>0.08624085208541266</v>
       </c>
       <c r="C11">
-        <v>1816.508948918692</v>
+        <v>1800.41371138818</v>
       </c>
       <c r="D11">
-        <v>1828.507948918692</v>
+        <v>1833.62371138818</v>
       </c>
       <c r="E11">
-        <v>-881.7009999999999</v>
+        <v>-860.4899999999999</v>
       </c>
       <c r="F11">
-        <v>190.899</v>
+        <v>212.11</v>
       </c>
       <c r="G11">
         <v>178.9</v>
@@ -2320,28 +2320,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M11">
-        <v>10.2130965</v>
+        <v>11.347885</v>
       </c>
       <c r="N11">
-        <v>82.92023683333335</v>
+        <v>81.78544833333335</v>
       </c>
       <c r="O11">
-        <v>16.58404736666667</v>
+        <v>16.35708966666667</v>
       </c>
       <c r="P11">
-        <v>66.33618946666668</v>
+        <v>65.42835866666668</v>
       </c>
       <c r="Q11">
-        <v>152.5361894666667</v>
+        <v>151.6283586666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09066153481484102</v>
+        <v>0.09106761342823627</v>
       </c>
       <c r="T11">
-        <v>0.9224003733766423</v>
+        <v>0.9307497770731947</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.119010413084156</v>
+        <v>8.20710937177574</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08624085208541266</v>
+        <v>0.08619810748931997</v>
       </c>
       <c r="C12">
-        <v>1800.41371138818</v>
+        <v>1781.142839522895</v>
       </c>
       <c r="D12">
-        <v>1833.62371138818</v>
+        <v>1835.563839522894</v>
       </c>
       <c r="E12">
-        <v>-860.4899999999999</v>
+        <v>-839.2789999999999</v>
       </c>
       <c r="F12">
-        <v>212.11</v>
+        <v>233.321</v>
       </c>
       <c r="G12">
         <v>178.9</v>
@@ -2402,45 +2402,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M12">
-        <v>11.347885</v>
+        <v>12.6693303</v>
       </c>
       <c r="N12">
-        <v>81.78544833333335</v>
+        <v>80.46400303333336</v>
       </c>
       <c r="O12">
-        <v>16.35708966666667</v>
+        <v>16.09280060666667</v>
       </c>
       <c r="P12">
-        <v>65.42835866666668</v>
+        <v>64.37120242666668</v>
       </c>
       <c r="Q12">
-        <v>151.6283586666667</v>
+        <v>150.5712024266667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09106761342823627</v>
+        <v>0.09148281740373029</v>
       </c>
       <c r="T12">
-        <v>0.930749777073195</v>
+        <v>0.939286807819108</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.20710937177574</v>
+        <v>7.351085742340568</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08619810748931997</v>
+        <v>0.08609136289322729</v>
       </c>
       <c r="C13">
-        <v>1781.142839522895</v>
+        <v>1764.794830163629</v>
       </c>
       <c r="D13">
-        <v>1835.563839522894</v>
+        <v>1840.426830163629</v>
       </c>
       <c r="E13">
-        <v>-839.2789999999999</v>
+        <v>-818.068</v>
       </c>
       <c r="F13">
-        <v>233.321</v>
+        <v>254.532</v>
       </c>
       <c r="G13">
         <v>178.9</v>
@@ -2484,28 +2484,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M13">
-        <v>12.6693303</v>
+        <v>13.8210876</v>
       </c>
       <c r="N13">
-        <v>80.46400303333336</v>
+        <v>79.31224573333336</v>
       </c>
       <c r="O13">
-        <v>16.09280060666667</v>
+        <v>15.86244914666667</v>
       </c>
       <c r="P13">
-        <v>64.37120242666668</v>
+        <v>63.44979658666669</v>
       </c>
       <c r="Q13">
-        <v>150.5712024266667</v>
+        <v>149.6497965866667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09148281740373029</v>
+        <v>0.09190745783321283</v>
       </c>
       <c r="T13">
-        <v>0.939286807819108</v>
+        <v>0.9480178619910649</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.351085742340568</v>
+        <v>6.738495263812188</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08609136289322729</v>
+        <v>0.08598461829713461</v>
       </c>
       <c r="C14">
-        <v>1764.794830163629</v>
+        <v>1748.472656459584</v>
       </c>
       <c r="D14">
-        <v>1840.426830163629</v>
+        <v>1845.315656459584</v>
       </c>
       <c r="E14">
-        <v>-818.068</v>
+        <v>-796.857</v>
       </c>
       <c r="F14">
-        <v>254.532</v>
+        <v>275.743</v>
       </c>
       <c r="G14">
         <v>178.9</v>
@@ -2566,28 +2566,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M14">
-        <v>13.8210876</v>
+        <v>14.9728449</v>
       </c>
       <c r="N14">
-        <v>79.31224573333336</v>
+        <v>78.16048843333336</v>
       </c>
       <c r="O14">
-        <v>15.86244914666667</v>
+        <v>15.63209768666667</v>
       </c>
       <c r="P14">
-        <v>63.44979658666669</v>
+        <v>62.52839074666669</v>
       </c>
       <c r="Q14">
-        <v>149.6497965866667</v>
+        <v>148.7283907466667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09190745783321283</v>
+        <v>0.09234186011164897</v>
       </c>
       <c r="T14">
-        <v>0.9480178619910649</v>
+        <v>0.956949630052032</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.738495263812188</v>
+        <v>6.220149474288173</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08598461829713461</v>
+        <v>0.08598987370104191</v>
       </c>
       <c r="C15">
-        <v>1748.472656459584</v>
+        <v>1727.020354902299</v>
       </c>
       <c r="D15">
-        <v>1845.315656459584</v>
+        <v>1845.074354902298</v>
       </c>
       <c r="E15">
-        <v>-796.857</v>
+        <v>-775.646</v>
       </c>
       <c r="F15">
-        <v>275.743</v>
+        <v>296.954</v>
       </c>
       <c r="G15">
         <v>178.9</v>
@@ -2648,45 +2648,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M15">
-        <v>14.9728449</v>
+        <v>16.4215562</v>
       </c>
       <c r="N15">
-        <v>78.16048843333336</v>
+        <v>76.71177713333336</v>
       </c>
       <c r="O15">
-        <v>15.63209768666667</v>
+        <v>15.34235542666667</v>
       </c>
       <c r="P15">
-        <v>62.52839074666669</v>
+        <v>61.36942170666669</v>
       </c>
       <c r="Q15">
-        <v>148.7283907466667</v>
+        <v>147.5694217066667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09234186011164897</v>
+        <v>0.0927863647686534</v>
       </c>
       <c r="T15">
-        <v>0.956949630052032</v>
+        <v>0.9660891136493009</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.220149474288173</v>
+        <v>5.671407277060219</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08598987370104191</v>
+        <v>0.08589112910494924</v>
       </c>
       <c r="C16">
-        <v>1727.020354902299</v>
+        <v>1710.353779716547</v>
       </c>
       <c r="D16">
-        <v>1845.074354902298</v>
+        <v>1849.618779716547</v>
       </c>
       <c r="E16">
-        <v>-775.646</v>
+        <v>-754.4349999999999</v>
       </c>
       <c r="F16">
-        <v>296.954</v>
+        <v>318.165</v>
       </c>
       <c r="G16">
         <v>178.9</v>
@@ -2730,28 +2730,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M16">
-        <v>16.4215562</v>
+        <v>17.5945245</v>
       </c>
       <c r="N16">
-        <v>76.71177713333336</v>
+        <v>75.53880883333335</v>
       </c>
       <c r="O16">
-        <v>15.34235542666667</v>
+        <v>15.10776176666667</v>
       </c>
       <c r="P16">
-        <v>61.36942170666669</v>
+        <v>60.43104706666668</v>
       </c>
       <c r="Q16">
-        <v>147.5694217066667</v>
+        <v>146.6310470666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0927863647686534</v>
+        <v>0.09324132835876381</v>
       </c>
       <c r="T16">
-        <v>0.9660891136493009</v>
+        <v>0.9754436439194466</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.671407277060219</v>
+        <v>5.293313458589537</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08589112910494924</v>
+        <v>0.08579238450885655</v>
       </c>
       <c r="C17">
-        <v>1710.353779716547</v>
+        <v>1693.709645672942</v>
       </c>
       <c r="D17">
-        <v>1849.618779716547</v>
+        <v>1854.185645672942</v>
       </c>
       <c r="E17">
-        <v>-754.4349999999999</v>
+        <v>-733.2239999999999</v>
       </c>
       <c r="F17">
-        <v>318.165</v>
+        <v>339.376</v>
       </c>
       <c r="G17">
         <v>178.9</v>
@@ -2812,28 +2812,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M17">
-        <v>17.5945245</v>
+        <v>18.7674928</v>
       </c>
       <c r="N17">
-        <v>75.53880883333335</v>
+        <v>74.36584053333335</v>
       </c>
       <c r="O17">
-        <v>15.10776176666667</v>
+        <v>14.87316810666667</v>
       </c>
       <c r="P17">
-        <v>60.43104706666668</v>
+        <v>59.49267242666669</v>
       </c>
       <c r="Q17">
-        <v>146.6310470666667</v>
+        <v>145.6926724266667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09324132835876381</v>
+        <v>0.09370712441530543</v>
       </c>
       <c r="T17">
-        <v>0.9754436439194466</v>
+        <v>0.9850209011007862</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.293313458589537</v>
+        <v>4.962481367427692</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08579238450885655</v>
+        <v>0.08569363991276388</v>
       </c>
       <c r="C18">
-        <v>1693.709645672942</v>
+        <v>1677.088119410189</v>
       </c>
       <c r="D18">
-        <v>1854.185645672942</v>
+        <v>1858.775119410189</v>
       </c>
       <c r="E18">
-        <v>-733.2239999999999</v>
+        <v>-712.0129999999999</v>
       </c>
       <c r="F18">
-        <v>339.376</v>
+        <v>360.587</v>
       </c>
       <c r="G18">
         <v>178.9</v>
@@ -2894,28 +2894,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M18">
-        <v>18.7674928</v>
+        <v>19.9404611</v>
       </c>
       <c r="N18">
-        <v>74.36584053333335</v>
+        <v>73.19287223333336</v>
       </c>
       <c r="O18">
-        <v>14.87316810666667</v>
+        <v>14.63857444666667</v>
       </c>
       <c r="P18">
-        <v>59.49267242666669</v>
+        <v>58.55429778666669</v>
       </c>
       <c r="Q18">
-        <v>145.6926724266667</v>
+        <v>144.7542977866667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09370712441530543</v>
+        <v>0.0941841444732095</v>
       </c>
       <c r="T18">
-        <v>0.9850209011007862</v>
+        <v>0.9948289355636041</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.962481367427692</v>
+        <v>4.670570698755474</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08569363991276388</v>
+        <v>0.08595489531667121</v>
       </c>
       <c r="C19">
-        <v>1677.088119410189</v>
+        <v>1643.783574133462</v>
       </c>
       <c r="D19">
-        <v>1858.775119410189</v>
+        <v>1846.681574133462</v>
       </c>
       <c r="E19">
-        <v>-712.0129999999999</v>
+        <v>-690.8019999999999</v>
       </c>
       <c r="F19">
-        <v>360.587</v>
+        <v>381.798</v>
       </c>
       <c r="G19">
         <v>178.9</v>
@@ -2976,45 +2976,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M19">
-        <v>19.9404611</v>
+        <v>22.0679244</v>
       </c>
       <c r="N19">
-        <v>73.19287223333336</v>
+        <v>71.06540893333334</v>
       </c>
       <c r="O19">
-        <v>14.63857444666667</v>
+        <v>14.21308178666667</v>
       </c>
       <c r="P19">
-        <v>58.55429778666669</v>
+        <v>56.85232714666667</v>
       </c>
       <c r="Q19">
-        <v>144.7542977866667</v>
+        <v>143.0523271466667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0941841444732095</v>
+        <v>0.09467279916667221</v>
       </c>
       <c r="T19">
-        <v>0.9948289355636041</v>
+        <v>1.004876190379174</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.670570698755474</v>
+        <v>4.220303262110747</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08595489531667122</v>
+        <v>0.08640815072057854</v>
       </c>
       <c r="C20">
-        <v>1643.783574133461</v>
+        <v>1601.960495328604</v>
       </c>
       <c r="D20">
-        <v>1846.681574133461</v>
+        <v>1826.069495328604</v>
       </c>
       <c r="E20">
-        <v>-690.8019999999999</v>
+        <v>-669.5909999999999</v>
       </c>
       <c r="F20">
-        <v>381.7979999999999</v>
+        <v>403.009</v>
       </c>
       <c r="G20">
         <v>178.9</v>
@@ -3058,45 +3058,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M20">
-        <v>22.0679244</v>
+        <v>24.7044517</v>
       </c>
       <c r="N20">
-        <v>71.06540893333336</v>
+        <v>68.42888163333336</v>
       </c>
       <c r="O20">
-        <v>14.21308178666667</v>
+        <v>13.68577632666667</v>
       </c>
       <c r="P20">
-        <v>56.85232714666669</v>
+        <v>54.74310530666669</v>
       </c>
       <c r="Q20">
-        <v>143.0523271466667</v>
+        <v>140.9431053066667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09467279916667221</v>
+        <v>0.09517351940812166</v>
       </c>
       <c r="T20">
-        <v>1.004876190379173</v>
+        <v>1.01517152556056</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.220303262110748</v>
+        <v>3.769900844766911</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08640815072057854</v>
+        <v>0.08635740612448585</v>
       </c>
       <c r="C21">
-        <v>1601.960495328604</v>
+        <v>1583.034236090704</v>
       </c>
       <c r="D21">
-        <v>1826.069495328604</v>
+        <v>1828.354236090704</v>
       </c>
       <c r="E21">
-        <v>-669.5909999999999</v>
+        <v>-648.3799999999999</v>
       </c>
       <c r="F21">
-        <v>403.009</v>
+        <v>424.22</v>
       </c>
       <c r="G21">
         <v>178.9</v>
@@ -3140,28 +3140,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M21">
-        <v>24.7044517</v>
+        <v>26.004686</v>
       </c>
       <c r="N21">
-        <v>68.42888163333336</v>
+        <v>67.12864733333335</v>
       </c>
       <c r="O21">
-        <v>13.68577632666667</v>
+        <v>13.42572946666667</v>
       </c>
       <c r="P21">
-        <v>54.74310530666669</v>
+        <v>53.70291786666668</v>
       </c>
       <c r="Q21">
-        <v>140.9431053066667</v>
+        <v>139.9029178666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09517351940812166</v>
+        <v>0.09568675765560732</v>
       </c>
       <c r="T21">
-        <v>1.01517152556056</v>
+        <v>1.02572424412148</v>
       </c>
       <c r="U21">
         <v>0.0613</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.769900844766911</v>
+        <v>3.581405802528565</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08635740612448585</v>
+        <v>0.08677706152839318</v>
       </c>
       <c r="C22">
-        <v>1583.034236090704</v>
+        <v>1543.09864465311</v>
       </c>
       <c r="D22">
-        <v>1828.354236090704</v>
+        <v>1809.62964465311</v>
       </c>
       <c r="E22">
-        <v>-648.3799999999999</v>
+        <v>-627.1689999999999</v>
       </c>
       <c r="F22">
-        <v>424.22</v>
+        <v>445.431</v>
       </c>
       <c r="G22">
         <v>178.9</v>
@@ -3222,45 +3222,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M22">
-        <v>26.004686</v>
+        <v>28.5521271</v>
       </c>
       <c r="N22">
-        <v>67.12864733333335</v>
+        <v>64.58120623333335</v>
       </c>
       <c r="O22">
-        <v>13.42572946666667</v>
+        <v>12.91624124666667</v>
       </c>
       <c r="P22">
-        <v>53.70291786666668</v>
+        <v>51.66496498666667</v>
       </c>
       <c r="Q22">
-        <v>139.9029178666667</v>
+        <v>137.8649649866667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09568675765560732</v>
+        <v>0.09621298927644706</v>
       </c>
       <c r="T22">
-        <v>1.02572424412148</v>
+        <v>1.036544120114323</v>
       </c>
       <c r="U22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.581405802528565</v>
+        <v>3.261870227991992</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08677706152839318</v>
+        <v>0.0867487169323005</v>
       </c>
       <c r="C23">
-        <v>1543.09864465311</v>
+        <v>1523.140265618983</v>
       </c>
       <c r="D23">
-        <v>1809.62964465311</v>
+        <v>1810.882265618983</v>
       </c>
       <c r="E23">
-        <v>-627.1689999999999</v>
+        <v>-605.9579999999999</v>
       </c>
       <c r="F23">
-        <v>445.431</v>
+        <v>466.642</v>
       </c>
       <c r="G23">
         <v>178.9</v>
@@ -3304,28 +3304,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M23">
-        <v>28.5521271</v>
+        <v>29.9117522</v>
       </c>
       <c r="N23">
-        <v>64.58120623333335</v>
+        <v>63.22158113333335</v>
       </c>
       <c r="O23">
-        <v>12.91624124666667</v>
+        <v>12.64431622666667</v>
       </c>
       <c r="P23">
-        <v>51.66496498666667</v>
+        <v>50.57726490666668</v>
       </c>
       <c r="Q23">
-        <v>137.8649649866667</v>
+        <v>136.7772649066667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09621298927644706</v>
+        <v>0.09675271401576988</v>
       </c>
       <c r="T23">
-        <v>1.036544120114323</v>
+        <v>1.04764142882493</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.261870227991992</v>
+        <v>3.113603399446902</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0867487169323005</v>
+        <v>0.08815557233620783</v>
       </c>
       <c r="C24">
-        <v>1523.140265618983</v>
+        <v>1441.780166912362</v>
       </c>
       <c r="D24">
-        <v>1810.882265618983</v>
+        <v>1750.733166912362</v>
       </c>
       <c r="E24">
-        <v>-605.9579999999999</v>
+        <v>-584.7469999999998</v>
       </c>
       <c r="F24">
-        <v>466.642</v>
+        <v>487.853</v>
       </c>
       <c r="G24">
         <v>178.9</v>
@@ -3386,45 +3386,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M24">
-        <v>29.9117522</v>
+        <v>35.0766307</v>
       </c>
       <c r="N24">
-        <v>63.22158113333335</v>
+        <v>58.05670263333335</v>
       </c>
       <c r="O24">
-        <v>12.64431622666667</v>
+        <v>11.61134052666667</v>
       </c>
       <c r="P24">
-        <v>50.57726490666668</v>
+        <v>46.44536210666668</v>
       </c>
       <c r="Q24">
-        <v>136.7772649066667</v>
+        <v>132.6453621066667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09675271401576988</v>
+        <v>0.09730645757949066</v>
       </c>
       <c r="T24">
-        <v>1.04764142882493</v>
+        <v>1.059026979320229</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.113603399446902</v>
+        <v>2.655139090463821</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08815557233620783</v>
+        <v>0.08818962774011514</v>
       </c>
       <c r="C25">
-        <v>1441.780166912362</v>
+        <v>1419.162645357168</v>
       </c>
       <c r="D25">
-        <v>1750.733166912362</v>
+        <v>1749.326645357168</v>
       </c>
       <c r="E25">
-        <v>-584.7469999999998</v>
+        <v>-563.5359999999998</v>
       </c>
       <c r="F25">
-        <v>487.853</v>
+        <v>509.064</v>
       </c>
       <c r="G25">
         <v>178.9</v>
@@ -3468,28 +3468,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M25">
-        <v>35.0766307</v>
+        <v>36.60170160000001</v>
       </c>
       <c r="N25">
-        <v>58.05670263333335</v>
+        <v>56.53163173333335</v>
       </c>
       <c r="O25">
-        <v>11.61134052666667</v>
+        <v>11.30632634666667</v>
       </c>
       <c r="P25">
-        <v>46.44536210666668</v>
+        <v>45.22530538666668</v>
       </c>
       <c r="Q25">
-        <v>132.6453621066667</v>
+        <v>131.4253053866667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09730645757949066</v>
+        <v>0.09787477334225676</v>
       </c>
       <c r="T25">
-        <v>1.059026979320229</v>
+        <v>1.070712149565405</v>
       </c>
       <c r="U25">
         <v>0.07190000000000001</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.655139090463821</v>
+        <v>2.544508295027828</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08818962774011514</v>
+        <v>0.08900368314402246</v>
       </c>
       <c r="C26">
-        <v>1419.162645357168</v>
+        <v>1364.990362771493</v>
       </c>
       <c r="D26">
-        <v>1749.326645357168</v>
+        <v>1716.365362771493</v>
       </c>
       <c r="E26">
-        <v>-563.5359999999999</v>
+        <v>-542.3249999999999</v>
       </c>
       <c r="F26">
-        <v>509.064</v>
+        <v>530.275</v>
       </c>
       <c r="G26">
         <v>178.9</v>
@@ -3550,45 +3550,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M26">
-        <v>36.6017016</v>
+        <v>40.194845</v>
       </c>
       <c r="N26">
-        <v>56.53163173333336</v>
+        <v>52.93848833333335</v>
       </c>
       <c r="O26">
-        <v>11.30632634666667</v>
+        <v>10.58769766666667</v>
       </c>
       <c r="P26">
-        <v>45.22530538666668</v>
+        <v>42.35079066666668</v>
       </c>
       <c r="Q26">
-        <v>131.4253053866667</v>
+        <v>128.5507906666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09787477334225675</v>
+        <v>0.09845824419202995</v>
       </c>
       <c r="T26">
-        <v>1.070712149565404</v>
+        <v>1.082708924350451</v>
       </c>
       <c r="U26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.544508295027829</v>
+        <v>2.317046709182069</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08900368314402246</v>
+        <v>0.08906893854792979</v>
       </c>
       <c r="C27">
-        <v>1364.990362771493</v>
+        <v>1341.190851965384</v>
       </c>
       <c r="D27">
-        <v>1716.365362771493</v>
+        <v>1713.776851965384</v>
       </c>
       <c r="E27">
-        <v>-542.3249999999999</v>
+        <v>-521.1139999999999</v>
       </c>
       <c r="F27">
-        <v>530.275</v>
+        <v>551.486</v>
       </c>
       <c r="G27">
         <v>178.9</v>
@@ -3632,28 +3632,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M27">
-        <v>40.194845</v>
+        <v>41.8026388</v>
       </c>
       <c r="N27">
-        <v>52.93848833333335</v>
+        <v>51.33069453333335</v>
       </c>
       <c r="O27">
-        <v>10.58769766666667</v>
+        <v>10.26613890666667</v>
       </c>
       <c r="P27">
-        <v>42.35079066666668</v>
+        <v>41.06455562666668</v>
       </c>
       <c r="Q27">
-        <v>128.5507906666667</v>
+        <v>127.2645556266667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09845824419202995</v>
+        <v>0.09905748452422944</v>
       </c>
       <c r="T27">
-        <v>1.082708924350451</v>
+        <v>1.09502993629185</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.317046709182069</v>
+        <v>2.227929528059682</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08906893854792979</v>
+        <v>0.08913419395183711</v>
       </c>
       <c r="C28">
-        <v>1341.190851965384</v>
+        <v>1317.399137049899</v>
       </c>
       <c r="D28">
-        <v>1713.776851965384</v>
+        <v>1711.196137049899</v>
       </c>
       <c r="E28">
-        <v>-521.1139999999999</v>
+        <v>-499.9029999999999</v>
       </c>
       <c r="F28">
-        <v>551.486</v>
+        <v>572.697</v>
       </c>
       <c r="G28">
         <v>178.9</v>
@@ -3714,28 +3714,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M28">
-        <v>41.8026388</v>
+        <v>43.41043260000001</v>
       </c>
       <c r="N28">
-        <v>51.33069453333335</v>
+        <v>49.72290073333335</v>
       </c>
       <c r="O28">
-        <v>10.26613890666667</v>
+        <v>9.94458014666667</v>
       </c>
       <c r="P28">
-        <v>41.06455562666668</v>
+        <v>39.77832058666668</v>
       </c>
       <c r="Q28">
-        <v>127.2645556266667</v>
+        <v>125.9783205866667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09905748452422944</v>
+        <v>0.09967314239977686</v>
       </c>
       <c r="T28">
-        <v>1.09502993629185</v>
+        <v>1.107688510204247</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.227929528059682</v>
+        <v>2.145413619613027</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08913419395183711</v>
+        <v>0.08919944935574442</v>
       </c>
       <c r="C29">
-        <v>1317.399137049899</v>
+        <v>1293.61518285934</v>
       </c>
       <c r="D29">
-        <v>1711.196137049899</v>
+        <v>1708.62318285934</v>
       </c>
       <c r="E29">
-        <v>-499.9029999999999</v>
+        <v>-478.6919999999999</v>
       </c>
       <c r="F29">
-        <v>572.697</v>
+        <v>593.908</v>
       </c>
       <c r="G29">
         <v>178.9</v>
@@ -3796,28 +3796,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M29">
-        <v>43.41043260000001</v>
+        <v>45.0182264</v>
       </c>
       <c r="N29">
-        <v>49.72290073333335</v>
+        <v>48.11510693333335</v>
       </c>
       <c r="O29">
-        <v>9.94458014666667</v>
+        <v>9.623021386666672</v>
       </c>
       <c r="P29">
-        <v>39.77832058666668</v>
+        <v>38.49208554666668</v>
       </c>
       <c r="Q29">
-        <v>125.9783205866667</v>
+        <v>124.6920855466667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09967314239977686</v>
+        <v>0.1003059018829784</v>
       </c>
       <c r="T29">
-        <v>1.107688510204247</v>
+        <v>1.120698711169765</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.145413619613027</v>
+        <v>2.068791704626848</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08919944935574442</v>
+        <v>0.09255910475965173</v>
       </c>
       <c r="C30">
-        <v>1293.61518285934</v>
+        <v>1149.639105575652</v>
       </c>
       <c r="D30">
-        <v>1708.62318285934</v>
+        <v>1585.858105575652</v>
       </c>
       <c r="E30">
-        <v>-478.6919999999999</v>
+        <v>-457.4809999999999</v>
       </c>
       <c r="F30">
-        <v>593.908</v>
+        <v>615.119</v>
       </c>
       <c r="G30">
         <v>178.9</v>
@@ -3878,45 +3878,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M30">
-        <v>45.0182264</v>
+        <v>55.36071</v>
       </c>
       <c r="N30">
-        <v>48.11510693333335</v>
+        <v>37.77262333333336</v>
       </c>
       <c r="O30">
-        <v>9.623021386666672</v>
+        <v>7.554524666666672</v>
       </c>
       <c r="P30">
-        <v>38.49208554666668</v>
+        <v>30.21809866666668</v>
       </c>
       <c r="Q30">
-        <v>124.6920855466667</v>
+        <v>116.4180986666667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1003059018829784</v>
+        <v>0.1009564855769743</v>
       </c>
       <c r="T30">
-        <v>1.120698711169765</v>
+        <v>1.134075396669524</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.068791704626848</v>
+        <v>1.68230019689656</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09255910475965173</v>
+        <v>0.09273796016355906</v>
       </c>
       <c r="C31">
-        <v>1149.639105575652</v>
+        <v>1122.385250474492</v>
       </c>
       <c r="D31">
-        <v>1585.858105575652</v>
+        <v>1579.815250474491</v>
       </c>
       <c r="E31">
-        <v>-457.481</v>
+        <v>-436.27</v>
       </c>
       <c r="F31">
-        <v>615.1189999999999</v>
+        <v>636.3299999999999</v>
       </c>
       <c r="G31">
         <v>178.9</v>
@@ -3960,28 +3960,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M31">
-        <v>55.36070999999999</v>
+        <v>57.26969999999999</v>
       </c>
       <c r="N31">
-        <v>37.77262333333336</v>
+        <v>35.86363333333336</v>
       </c>
       <c r="O31">
-        <v>7.554524666666673</v>
+        <v>7.172726666666673</v>
       </c>
       <c r="P31">
-        <v>30.21809866666669</v>
+        <v>28.69090666666669</v>
       </c>
       <c r="Q31">
-        <v>116.4180986666667</v>
+        <v>114.8909066666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1009564855769743</v>
+        <v>0.101625657376513</v>
       </c>
       <c r="T31">
-        <v>1.134075396669524</v>
+        <v>1.147834273183561</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.68230019689656</v>
+        <v>1.626223523666675</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09273796016355906</v>
+        <v>0.09291681556746639</v>
       </c>
       <c r="C32">
-        <v>1122.385250474492</v>
+        <v>1095.17727272208</v>
       </c>
       <c r="D32">
-        <v>1579.815250474491</v>
+        <v>1573.81827272208</v>
       </c>
       <c r="E32">
-        <v>-436.27</v>
+        <v>-415.059</v>
       </c>
       <c r="F32">
-        <v>636.3299999999999</v>
+        <v>657.5409999999999</v>
       </c>
       <c r="G32">
         <v>178.9</v>
@@ -4042,28 +4042,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M32">
-        <v>57.26969999999999</v>
+        <v>59.17868999999999</v>
       </c>
       <c r="N32">
-        <v>35.86363333333336</v>
+        <v>33.95464333333337</v>
       </c>
       <c r="O32">
-        <v>7.172726666666673</v>
+        <v>6.790928666666673</v>
       </c>
       <c r="P32">
-        <v>28.69090666666669</v>
+        <v>27.16371466666669</v>
       </c>
       <c r="Q32">
-        <v>114.8909066666667</v>
+        <v>113.3637146666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.101625657376513</v>
+        <v>0.1023142254600962</v>
       </c>
       <c r="T32">
-        <v>1.147834273183561</v>
+        <v>1.161991957712498</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.626223523666675</v>
+        <v>1.573764700322589</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09291681556746639</v>
+        <v>0.0930956709713737</v>
       </c>
       <c r="C33">
-        <v>1095.17727272208</v>
+        <v>1068.014651842977</v>
       </c>
       <c r="D33">
-        <v>1573.81827272208</v>
+        <v>1567.866651842977</v>
       </c>
       <c r="E33">
-        <v>-415.059</v>
+        <v>-393.848</v>
       </c>
       <c r="F33">
-        <v>657.5409999999999</v>
+        <v>678.752</v>
       </c>
       <c r="G33">
         <v>178.9</v>
@@ -4124,28 +4124,28 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M33">
-        <v>59.17868999999999</v>
+        <v>61.08767999999999</v>
       </c>
       <c r="N33">
-        <v>33.95464333333337</v>
+        <v>32.04565333333336</v>
       </c>
       <c r="O33">
-        <v>6.790928666666673</v>
+        <v>6.409130666666673</v>
       </c>
       <c r="P33">
-        <v>27.16371466666669</v>
+        <v>25.63652266666669</v>
       </c>
       <c r="Q33">
-        <v>113.3637146666667</v>
+        <v>111.8365226666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1023142254600962</v>
+        <v>0.1030230455461378</v>
       </c>
       <c r="T33">
-        <v>1.161991957712498</v>
+        <v>1.17656604472758</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.573764700322589</v>
+        <v>1.524584553437508</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0930956709713737</v>
+        <v>0.1094338273626434</v>
       </c>
       <c r="C34">
-        <v>1068.014651842977</v>
+        <v>644.2496704128894</v>
       </c>
       <c r="D34">
-        <v>1567.866651842977</v>
+        <v>1165.312670412889</v>
       </c>
       <c r="E34">
-        <v>-393.848</v>
+        <v>-372.6369999999999</v>
       </c>
       <c r="F34">
-        <v>678.752</v>
+        <v>699.963</v>
       </c>
       <c r="G34">
         <v>178.9</v>
@@ -4206,45 +4206,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M34">
-        <v>61.08767999999999</v>
+        <v>102.7545684</v>
       </c>
       <c r="N34">
-        <v>32.04565333333336</v>
+        <v>-9.621235066666657</v>
       </c>
       <c r="O34">
-        <v>6.409130666666673</v>
+        <v>-1.924247013333331</v>
       </c>
       <c r="P34">
-        <v>25.63652266666669</v>
+        <v>-7.696988053333325</v>
       </c>
       <c r="Q34">
-        <v>111.8365226666667</v>
+        <v>78.50301194666666</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1030230455461378</v>
+        <v>0.1041364692394678</v>
       </c>
       <c r="T34">
-        <v>1.17656604472758</v>
+        <v>1.199459207761187</v>
       </c>
       <c r="U34">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2</v>
+        <v>0.1812733677607143</v>
       </c>
       <c r="W34">
-        <v>0.07199999999999999</v>
+        <v>0.1201890696127271</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.524584553437508</v>
+        <v>0.9063668388035713</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1094338273626434</v>
+        <v>0.1104438273626434</v>
       </c>
       <c r="C35">
-        <v>644.2496704128894</v>
+        <v>604.8317379781129</v>
       </c>
       <c r="D35">
-        <v>1165.312670412889</v>
+        <v>1147.105737978113</v>
       </c>
       <c r="E35">
-        <v>-372.6369999999999</v>
+        <v>-351.4259999999999</v>
       </c>
       <c r="F35">
-        <v>699.963</v>
+        <v>721.174</v>
       </c>
       <c r="G35">
         <v>178.9</v>
@@ -4288,37 +4288,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M35">
-        <v>102.7545684</v>
+        <v>105.8683432</v>
       </c>
       <c r="N35">
-        <v>-9.621235066666657</v>
+        <v>-12.73500986666666</v>
       </c>
       <c r="O35">
-        <v>-1.924247013333331</v>
+        <v>-2.547001973333332</v>
       </c>
       <c r="P35">
-        <v>-7.696988053333325</v>
+        <v>-10.18800789333333</v>
       </c>
       <c r="Q35">
-        <v>78.50301194666666</v>
+        <v>76.01199210666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1041364692394678</v>
+        <v>0.1050203551370355</v>
       </c>
       <c r="T35">
-        <v>1.199459207761187</v>
+        <v>1.217632832121205</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.1812733677607143</v>
+        <v>0.1759417981206933</v>
       </c>
       <c r="W35">
-        <v>0.1201890696127271</v>
+        <v>0.1209717440358822</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.9063668388035713</v>
+        <v>0.8797089906034663</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1104438273626434</v>
+        <v>0.1114538273626434</v>
       </c>
       <c r="C36">
-        <v>604.8317379781129</v>
+        <v>565.9739861907658</v>
       </c>
       <c r="D36">
-        <v>1147.105737978113</v>
+        <v>1129.458986190766</v>
       </c>
       <c r="E36">
-        <v>-351.4259999999999</v>
+        <v>-330.2149999999999</v>
       </c>
       <c r="F36">
-        <v>721.174</v>
+        <v>742.385</v>
       </c>
       <c r="G36">
         <v>178.9</v>
@@ -4370,37 +4370,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M36">
-        <v>105.8683432</v>
+        <v>108.982118</v>
       </c>
       <c r="N36">
-        <v>-12.73500986666666</v>
+        <v>-15.84878466666666</v>
       </c>
       <c r="O36">
-        <v>-2.547001973333332</v>
+        <v>-3.169756933333332</v>
       </c>
       <c r="P36">
-        <v>-10.18800789333333</v>
+        <v>-12.67902773333333</v>
       </c>
       <c r="Q36">
-        <v>76.01199210666667</v>
+        <v>73.52097226666666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1050203551370355</v>
+        <v>0.1059314375237591</v>
       </c>
       <c r="T36">
-        <v>1.217632832121205</v>
+        <v>1.23636564492307</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.1759417981206933</v>
+        <v>0.1709148896029592</v>
       </c>
       <c r="W36">
-        <v>0.1209717440358822</v>
+        <v>0.1217096942062856</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8797089906034663</v>
+        <v>0.8545744480147959</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1114538273626434</v>
+        <v>0.1124638273626434</v>
       </c>
       <c r="C37">
-        <v>565.9739861907658</v>
+        <v>527.6509537560378</v>
       </c>
       <c r="D37">
-        <v>1129.458986190766</v>
+        <v>1112.346953756038</v>
       </c>
       <c r="E37">
-        <v>-330.2149999999999</v>
+        <v>-309.0039999999999</v>
       </c>
       <c r="F37">
-        <v>742.385</v>
+        <v>763.596</v>
       </c>
       <c r="G37">
         <v>178.9</v>
@@ -4452,37 +4452,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M37">
-        <v>108.982118</v>
+        <v>112.0958928</v>
       </c>
       <c r="N37">
-        <v>-15.84878466666666</v>
+        <v>-18.96255946666666</v>
       </c>
       <c r="O37">
-        <v>-3.169756933333332</v>
+        <v>-3.792511893333332</v>
       </c>
       <c r="P37">
-        <v>-12.67902773333333</v>
+        <v>-15.17004757333333</v>
       </c>
       <c r="Q37">
-        <v>73.52097226666666</v>
+        <v>71.02995242666665</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1059314375237591</v>
+        <v>0.1068709912350679</v>
       </c>
       <c r="T37">
-        <v>1.23636564492307</v>
+        <v>1.255683858124993</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1709148896029592</v>
+        <v>0.1661672537806548</v>
       </c>
       <c r="W37">
-        <v>0.1217096942062856</v>
+        <v>0.1224066471449999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8545744480147959</v>
+        <v>0.8308362689032737</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1124638273626434</v>
+        <v>0.1134738273626434</v>
       </c>
       <c r="C38">
-        <v>527.6509537560379</v>
+        <v>489.8386993704497</v>
       </c>
       <c r="D38">
-        <v>1112.346953756038</v>
+        <v>1095.74569937045</v>
       </c>
       <c r="E38">
-        <v>-309.004</v>
+        <v>-287.793</v>
       </c>
       <c r="F38">
-        <v>763.5959999999999</v>
+        <v>784.8069999999999</v>
       </c>
       <c r="G38">
         <v>178.9</v>
@@ -4534,37 +4534,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M38">
-        <v>112.0958928</v>
+        <v>115.2096676</v>
       </c>
       <c r="N38">
-        <v>-18.96255946666665</v>
+        <v>-22.07633426666665</v>
       </c>
       <c r="O38">
-        <v>-3.79251189333333</v>
+        <v>-4.41526685333333</v>
       </c>
       <c r="P38">
-        <v>-15.17004757333332</v>
+        <v>-17.66106741333332</v>
       </c>
       <c r="Q38">
-        <v>71.02995242666667</v>
+        <v>68.53893258666668</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1068709912350679</v>
+        <v>0.1078403720483229</v>
       </c>
       <c r="T38">
-        <v>1.255683858124993</v>
+        <v>1.275615347936501</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1661672537806548</v>
+        <v>0.1616762469217181</v>
       </c>
       <c r="W38">
-        <v>0.1224066471449999</v>
+        <v>0.1230659269518918</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8308362689032738</v>
+        <v>0.8083812346085907</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1134738273626434</v>
+        <v>0.1356726054374361</v>
       </c>
       <c r="C39">
-        <v>489.8386993704497</v>
+        <v>197.9755302434932</v>
       </c>
       <c r="D39">
-        <v>1095.74569937045</v>
+        <v>825.0935302434932</v>
       </c>
       <c r="E39">
-        <v>-287.793</v>
+        <v>-266.5819999999999</v>
       </c>
       <c r="F39">
-        <v>784.8069999999999</v>
+        <v>806.018</v>
       </c>
       <c r="G39">
         <v>178.9</v>
@@ -4616,45 +4616,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M39">
-        <v>115.2096676</v>
+        <v>161.8484144</v>
       </c>
       <c r="N39">
-        <v>-22.07633426666665</v>
+        <v>-68.71508106666667</v>
       </c>
       <c r="O39">
-        <v>-4.41526685333333</v>
+        <v>-13.74301621333333</v>
       </c>
       <c r="P39">
-        <v>-17.66106741333332</v>
+        <v>-54.97206485333334</v>
       </c>
       <c r="Q39">
-        <v>68.53893258666668</v>
+        <v>31.22793514666665</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1078403720483229</v>
+        <v>0.1099196975245745</v>
       </c>
       <c r="T39">
-        <v>1.275615347936501</v>
+        <v>1.318368468256216</v>
       </c>
       <c r="U39">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1616762469217181</v>
+        <v>0.1150871124423365</v>
       </c>
       <c r="W39">
-        <v>0.1230659269518918</v>
+        <v>0.1776905078215788</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.8083812346085907</v>
+        <v>0.5754355622116822</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1356726054374361</v>
+        <v>0.1372226054374361</v>
       </c>
       <c r="C40">
-        <v>197.9755302434932</v>
+        <v>162.7757036752915</v>
       </c>
       <c r="D40">
-        <v>825.0935302434932</v>
+        <v>811.1047036752916</v>
       </c>
       <c r="E40">
-        <v>-266.5819999999999</v>
+        <v>-245.3709999999999</v>
       </c>
       <c r="F40">
-        <v>806.018</v>
+        <v>827.229</v>
       </c>
       <c r="G40">
         <v>178.9</v>
@@ -4698,37 +4698,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M40">
-        <v>161.8484144</v>
+        <v>166.1075832</v>
       </c>
       <c r="N40">
-        <v>-68.71508106666667</v>
+        <v>-72.97424986666667</v>
       </c>
       <c r="O40">
-        <v>-13.74301621333333</v>
+        <v>-14.59484997333333</v>
       </c>
       <c r="P40">
-        <v>-54.97206485333334</v>
+        <v>-58.37939989333334</v>
       </c>
       <c r="Q40">
-        <v>31.22793514666665</v>
+        <v>27.82060010666665</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1099196975245745</v>
+        <v>0.1109708401069446</v>
       </c>
       <c r="T40">
-        <v>1.318368468256216</v>
+        <v>1.339981066096482</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1150871124423365</v>
+        <v>0.1121361608412509</v>
       </c>
       <c r="W40">
-        <v>0.1776905078215788</v>
+        <v>0.1782830589030768</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5754355622116822</v>
+        <v>0.5606808042062545</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1372226054374361</v>
+        <v>0.1387726054374361</v>
       </c>
       <c r="C41">
-        <v>162.7757036752915</v>
+        <v>128.0423087205463</v>
       </c>
       <c r="D41">
-        <v>811.1047036752916</v>
+        <v>797.5823087205464</v>
       </c>
       <c r="E41">
-        <v>-245.3709999999999</v>
+        <v>-224.1599999999999</v>
       </c>
       <c r="F41">
-        <v>827.229</v>
+        <v>848.4400000000001</v>
       </c>
       <c r="G41">
         <v>178.9</v>
@@ -4780,37 +4780,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M41">
-        <v>166.1075832</v>
+        <v>170.366752</v>
       </c>
       <c r="N41">
-        <v>-72.97424986666667</v>
+        <v>-77.23341866666667</v>
       </c>
       <c r="O41">
-        <v>-14.59484997333333</v>
+        <v>-15.44668373333333</v>
       </c>
       <c r="P41">
-        <v>-58.37939989333334</v>
+        <v>-61.78673493333334</v>
       </c>
       <c r="Q41">
-        <v>27.82060010666665</v>
+        <v>24.41326506666665</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1109708401069446</v>
+        <v>0.1120570207753936</v>
       </c>
       <c r="T41">
-        <v>1.339981066096482</v>
+        <v>1.362314083864757</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1121361608412509</v>
+        <v>0.1093327568202196</v>
       </c>
       <c r="W41">
-        <v>0.1782830589030768</v>
+        <v>0.1788459824304999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5606808042062545</v>
+        <v>0.5466637841010982</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1387726054374361</v>
+        <v>0.1403226054374361</v>
       </c>
       <c r="C42">
-        <v>128.0423087205463</v>
+        <v>93.75239947131797</v>
       </c>
       <c r="D42">
-        <v>797.5823087205464</v>
+        <v>784.5033994713181</v>
       </c>
       <c r="E42">
-        <v>-224.1599999999999</v>
+        <v>-202.9489999999998</v>
       </c>
       <c r="F42">
-        <v>848.4400000000001</v>
+        <v>869.6510000000001</v>
       </c>
       <c r="G42">
         <v>178.9</v>
@@ -4862,37 +4862,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M42">
-        <v>170.366752</v>
+        <v>174.6259208</v>
       </c>
       <c r="N42">
-        <v>-77.23341866666667</v>
+        <v>-81.49258746666666</v>
       </c>
       <c r="O42">
-        <v>-15.44668373333333</v>
+        <v>-16.29851749333333</v>
       </c>
       <c r="P42">
-        <v>-61.78673493333334</v>
+        <v>-65.19406997333333</v>
       </c>
       <c r="Q42">
-        <v>24.41326506666665</v>
+        <v>21.00593002666666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1120570207753936</v>
+        <v>0.1131800211275189</v>
       </c>
       <c r="T42">
-        <v>1.362314083864757</v>
+        <v>1.385404153082804</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1093327568202196</v>
+        <v>0.1066661042148484</v>
       </c>
       <c r="W42">
-        <v>0.1788459824304999</v>
+        <v>0.1793814462736584</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5466637841010982</v>
+        <v>0.5333305210742422</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1403226054374361</v>
+        <v>0.1418726054374362</v>
       </c>
       <c r="C43">
-        <v>93.75239947131797</v>
+        <v>59.88451082294659</v>
       </c>
       <c r="D43">
-        <v>784.5033994713181</v>
+        <v>771.8465108229467</v>
       </c>
       <c r="E43">
-        <v>-202.9489999999998</v>
+        <v>-181.7379999999998</v>
       </c>
       <c r="F43">
-        <v>869.6510000000001</v>
+        <v>890.8620000000001</v>
       </c>
       <c r="G43">
         <v>178.9</v>
@@ -4944,37 +4944,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M43">
-        <v>174.6259208</v>
+        <v>178.8850896</v>
       </c>
       <c r="N43">
-        <v>-81.49258746666666</v>
+        <v>-85.75175626666666</v>
       </c>
       <c r="O43">
-        <v>-16.29851749333333</v>
+        <v>-17.15035125333333</v>
       </c>
       <c r="P43">
-        <v>-65.19406997333333</v>
+        <v>-68.60140501333333</v>
       </c>
       <c r="Q43">
-        <v>21.00593002666666</v>
+        <v>17.59859498666665</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1131800211275189</v>
+        <v>0.1143417456297176</v>
       </c>
       <c r="T43">
-        <v>1.385404153082804</v>
+        <v>1.409290431584232</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1066661042148484</v>
+        <v>0.1041264350668759</v>
       </c>
       <c r="W43">
-        <v>0.1793814462736584</v>
+        <v>0.1798914118385714</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5333305210742422</v>
+        <v>0.5206321753343792</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1418726054374361</v>
+        <v>0.1434226054374361</v>
       </c>
       <c r="C44">
-        <v>59.88451082294694</v>
+        <v>26.4185409170035</v>
       </c>
       <c r="D44">
-        <v>771.8465108229469</v>
+        <v>759.5915409170035</v>
       </c>
       <c r="E44">
-        <v>-181.7379999999999</v>
+        <v>-160.5269999999999</v>
       </c>
       <c r="F44">
-        <v>890.862</v>
+        <v>912.073</v>
       </c>
       <c r="G44">
         <v>178.9</v>
@@ -5026,37 +5026,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M44">
-        <v>178.8850896</v>
+        <v>183.1442584</v>
       </c>
       <c r="N44">
-        <v>-85.75175626666663</v>
+        <v>-90.01092506666666</v>
       </c>
       <c r="O44">
-        <v>-17.15035125333333</v>
+        <v>-18.00218501333333</v>
       </c>
       <c r="P44">
-        <v>-68.60140501333331</v>
+        <v>-72.00874005333333</v>
       </c>
       <c r="Q44">
-        <v>17.59859498666668</v>
+        <v>14.19125994666666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1143417456297176</v>
+        <v>0.1155442323951512</v>
       </c>
       <c r="T44">
-        <v>1.409290431584231</v>
+        <v>1.434014825120797</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1041264350668759</v>
+        <v>0.1017048900653206</v>
       </c>
       <c r="W44">
-        <v>0.1798914118385713</v>
+        <v>0.1803776580748836</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5206321753343793</v>
+        <v>0.5085244503266031</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1434226054374361</v>
+        <v>0.1606424654685583</v>
       </c>
       <c r="C45">
-        <v>26.4185409170035</v>
+        <v>-108.6881331444031</v>
       </c>
       <c r="D45">
-        <v>759.5915409170035</v>
+        <v>645.6958668555969</v>
       </c>
       <c r="E45">
-        <v>-160.5269999999999</v>
+        <v>-139.3159999999999</v>
       </c>
       <c r="F45">
-        <v>912.073</v>
+        <v>933.284</v>
       </c>
       <c r="G45">
         <v>178.9</v>
@@ -5108,45 +5108,45 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M45">
-        <v>183.1442584</v>
+        <v>220.0683672</v>
       </c>
       <c r="N45">
-        <v>-90.01092506666666</v>
+        <v>-126.9350338666667</v>
       </c>
       <c r="O45">
-        <v>-18.00218501333333</v>
+        <v>-25.38700677333333</v>
       </c>
       <c r="P45">
-        <v>-72.00874005333333</v>
+        <v>-101.5480270933333</v>
       </c>
       <c r="Q45">
-        <v>14.19125994666666</v>
+        <v>-15.34802709333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1155442323951512</v>
+        <v>0.1172715580292114</v>
       </c>
       <c r="T45">
-        <v>1.434014825120797</v>
+        <v>1.469530458198805</v>
       </c>
       <c r="U45">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1017048900653206</v>
+        <v>0.08464036382720375</v>
       </c>
       <c r="W45">
-        <v>0.1803776580748836</v>
+        <v>0.2158418022095454</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.5085244503266031</v>
+        <v>0.4232018191360187</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1606424654685583</v>
+        <v>0.1625424654685584</v>
       </c>
       <c r="C46">
-        <v>-108.6881331444031</v>
+        <v>-140.4079239438919</v>
       </c>
       <c r="D46">
-        <v>645.6958668555969</v>
+        <v>635.1870760561081</v>
       </c>
       <c r="E46">
-        <v>-139.3159999999999</v>
+        <v>-118.1049999999999</v>
       </c>
       <c r="F46">
-        <v>933.284</v>
+        <v>954.495</v>
       </c>
       <c r="G46">
         <v>178.9</v>
@@ -5190,37 +5190,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M46">
-        <v>220.0683672</v>
+        <v>225.069921</v>
       </c>
       <c r="N46">
-        <v>-126.9350338666667</v>
+        <v>-131.9365876666667</v>
       </c>
       <c r="O46">
-        <v>-25.38700677333333</v>
+        <v>-26.38731753333333</v>
       </c>
       <c r="P46">
-        <v>-101.5480270933333</v>
+        <v>-105.5492701333333</v>
       </c>
       <c r="Q46">
-        <v>-15.34802709333334</v>
+        <v>-19.34927013333335</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1172715580292114</v>
+        <v>0.1185710409024698</v>
       </c>
       <c r="T46">
-        <v>1.469530458198805</v>
+        <v>1.496249193802419</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.08464036382720375</v>
+        <v>0.08275946685326588</v>
       </c>
       <c r="W46">
-        <v>0.2158418022095454</v>
+        <v>0.2162853177159999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4232018191360187</v>
+        <v>0.4137973342663294</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1625424654685584</v>
+        <v>0.1644424654685583</v>
       </c>
       <c r="C47">
-        <v>-140.4079239438919</v>
+        <v>-171.7911286409228</v>
       </c>
       <c r="D47">
-        <v>635.1870760561081</v>
+        <v>625.0148713590772</v>
       </c>
       <c r="E47">
-        <v>-118.1049999999999</v>
+        <v>-96.89399999999989</v>
       </c>
       <c r="F47">
-        <v>954.495</v>
+        <v>975.706</v>
       </c>
       <c r="G47">
         <v>178.9</v>
@@ -5272,37 +5272,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M47">
-        <v>225.069921</v>
+        <v>230.0714748</v>
       </c>
       <c r="N47">
-        <v>-131.9365876666667</v>
+        <v>-136.9381414666667</v>
       </c>
       <c r="O47">
-        <v>-26.38731753333333</v>
+        <v>-27.38762829333333</v>
       </c>
       <c r="P47">
-        <v>-105.5492701333333</v>
+        <v>-109.5505131733333</v>
       </c>
       <c r="Q47">
-        <v>-19.34927013333335</v>
+        <v>-23.35051317333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1185710409024698</v>
+        <v>0.119918652771034</v>
       </c>
       <c r="T47">
-        <v>1.496249193802419</v>
+        <v>1.523957512206168</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.08275946685326588</v>
+        <v>0.08096034800862967</v>
       </c>
       <c r="W47">
-        <v>0.2162853177159999</v>
+        <v>0.2167095499395651</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4137973342663294</v>
+        <v>0.4048017400431483</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1644424654685583</v>
+        <v>0.1663424654685584</v>
       </c>
       <c r="C48">
-        <v>-171.7911286409228</v>
+        <v>-202.8536631268506</v>
       </c>
       <c r="D48">
-        <v>625.0148713590772</v>
+        <v>615.1633368731494</v>
       </c>
       <c r="E48">
-        <v>-96.89399999999989</v>
+        <v>-75.68299999999988</v>
       </c>
       <c r="F48">
-        <v>975.706</v>
+        <v>996.917</v>
       </c>
       <c r="G48">
         <v>178.9</v>
@@ -5354,37 +5354,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M48">
-        <v>230.0714748</v>
+        <v>235.0730286</v>
       </c>
       <c r="N48">
-        <v>-136.9381414666667</v>
+        <v>-141.9396952666667</v>
       </c>
       <c r="O48">
-        <v>-27.38762829333333</v>
+        <v>-28.38793905333333</v>
       </c>
       <c r="P48">
-        <v>-109.5505131733333</v>
+        <v>-113.5517562133333</v>
       </c>
       <c r="Q48">
-        <v>-23.35051317333333</v>
+        <v>-27.35175621333335</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.119918652771034</v>
+        <v>0.1213171179176573</v>
       </c>
       <c r="T48">
-        <v>1.523957512206168</v>
+        <v>1.552711427530812</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.08096034800862967</v>
+        <v>0.07923778741270138</v>
       </c>
       <c r="W48">
-        <v>0.2167095499395651</v>
+        <v>0.217115729728085</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4048017400431483</v>
+        <v>0.3961889370635069</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1663424654685584</v>
+        <v>0.1682424654685583</v>
       </c>
       <c r="C49">
-        <v>-202.8536631268506</v>
+        <v>-233.6104553941511</v>
       </c>
       <c r="D49">
-        <v>615.1633368731494</v>
+        <v>605.6175446058489</v>
       </c>
       <c r="E49">
-        <v>-75.68299999999988</v>
+        <v>-54.47199999999987</v>
       </c>
       <c r="F49">
-        <v>996.917</v>
+        <v>1018.128</v>
       </c>
       <c r="G49">
         <v>178.9</v>
@@ -5436,37 +5436,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M49">
-        <v>235.0730286</v>
+        <v>240.0745824</v>
       </c>
       <c r="N49">
-        <v>-141.9396952666667</v>
+        <v>-146.9412490666667</v>
       </c>
       <c r="O49">
-        <v>-28.38793905333333</v>
+        <v>-29.38824981333333</v>
       </c>
       <c r="P49">
-        <v>-113.5517562133333</v>
+        <v>-117.5529992533333</v>
       </c>
       <c r="Q49">
-        <v>-27.35175621333335</v>
+        <v>-31.35299925333335</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1213171179176573</v>
+        <v>0.1227693701853046</v>
       </c>
       <c r="T49">
-        <v>1.552711427530812</v>
+        <v>1.582571262675636</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07923778741270138</v>
+        <v>0.07758700017493676</v>
       </c>
       <c r="W49">
-        <v>0.217115729728085</v>
+        <v>0.2175049853587499</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3961889370635069</v>
+        <v>0.3879350008746838</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1682424654685583</v>
+        <v>0.1701424654685583</v>
       </c>
       <c r="C50">
-        <v>-233.610455394151</v>
+        <v>-264.0755210137689</v>
       </c>
       <c r="D50">
-        <v>605.6175446058489</v>
+        <v>596.363478986231</v>
       </c>
       <c r="E50">
-        <v>-54.47199999999998</v>
+        <v>-33.26099999999997</v>
       </c>
       <c r="F50">
-        <v>1018.128</v>
+        <v>1039.339</v>
       </c>
       <c r="G50">
         <v>178.9</v>
@@ -5518,37 +5518,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M50">
-        <v>240.0745824</v>
+        <v>245.0761362</v>
       </c>
       <c r="N50">
-        <v>-146.9412490666666</v>
+        <v>-151.9428028666667</v>
       </c>
       <c r="O50">
-        <v>-29.38824981333333</v>
+        <v>-30.38856057333333</v>
       </c>
       <c r="P50">
-        <v>-117.5529992533333</v>
+        <v>-121.5542422933333</v>
       </c>
       <c r="Q50">
-        <v>-31.35299925333332</v>
+        <v>-35.35424229333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1227693701853046</v>
+        <v>0.1242785735222713</v>
       </c>
       <c r="T50">
-        <v>1.582571262675636</v>
+        <v>1.613602071747707</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07758700017493678</v>
+        <v>0.07600359200810132</v>
       </c>
       <c r="W50">
-        <v>0.2175049853587499</v>
+        <v>0.2178783530044897</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3879350008746838</v>
+        <v>0.3800179600405066</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1701424654685583</v>
+        <v>0.1720424654685583</v>
       </c>
       <c r="C51">
-        <v>-264.0755210137689</v>
+        <v>-294.2620317966762</v>
       </c>
       <c r="D51">
-        <v>596.363478986231</v>
+        <v>587.3879682033238</v>
       </c>
       <c r="E51">
-        <v>-33.26099999999997</v>
+        <v>-12.04999999999995</v>
       </c>
       <c r="F51">
-        <v>1039.339</v>
+        <v>1060.55</v>
       </c>
       <c r="G51">
         <v>178.9</v>
@@ -5600,37 +5600,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M51">
-        <v>245.0761362</v>
+        <v>250.07769</v>
       </c>
       <c r="N51">
-        <v>-151.9428028666667</v>
+        <v>-156.9443566666666</v>
       </c>
       <c r="O51">
-        <v>-30.38856057333333</v>
+        <v>-31.38887133333333</v>
       </c>
       <c r="P51">
-        <v>-121.5542422933333</v>
+        <v>-125.5554853333333</v>
       </c>
       <c r="Q51">
-        <v>-35.35424229333333</v>
+        <v>-39.35548533333332</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1242785735222713</v>
+        <v>0.1258481449927168</v>
       </c>
       <c r="T51">
-        <v>1.613602071747707</v>
+        <v>1.645874113182661</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07600359200810132</v>
+        <v>0.0744835201679393</v>
       </c>
       <c r="W51">
-        <v>0.2178783530044897</v>
+        <v>0.2182367859443999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3800179600405066</v>
+        <v>0.3724176008396964</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1720424654685583</v>
+        <v>0.1739424654685583</v>
       </c>
       <c r="C52">
-        <v>-294.2620317966762</v>
+        <v>-324.1823783470605</v>
       </c>
       <c r="D52">
-        <v>587.3879682033238</v>
+        <v>578.6786216529395</v>
       </c>
       <c r="E52">
-        <v>-12.04999999999995</v>
+        <v>9.161000000000058</v>
       </c>
       <c r="F52">
-        <v>1060.55</v>
+        <v>1081.761</v>
       </c>
       <c r="G52">
         <v>178.9</v>
@@ -5682,37 +5682,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M52">
-        <v>250.07769</v>
+        <v>255.0792438</v>
       </c>
       <c r="N52">
-        <v>-156.9443566666666</v>
+        <v>-161.9459104666666</v>
       </c>
       <c r="O52">
-        <v>-31.38887133333333</v>
+        <v>-32.38918209333333</v>
       </c>
       <c r="P52">
-        <v>-125.5554853333333</v>
+        <v>-129.5567283733333</v>
       </c>
       <c r="Q52">
-        <v>-39.35548533333332</v>
+        <v>-43.35672837333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1258481449927168</v>
+        <v>0.127481780604813</v>
       </c>
       <c r="T52">
-        <v>1.645874113182661</v>
+        <v>1.679463380798634</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0744835201679393</v>
+        <v>0.07302305898817578</v>
       </c>
       <c r="W52">
-        <v>0.2182367859443999</v>
+        <v>0.2185811626905882</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3724176008396964</v>
+        <v>0.3651152949408789</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1739424654685583</v>
+        <v>0.1758424654685583</v>
       </c>
       <c r="C53">
-        <v>-324.1823783470605</v>
+        <v>-353.8482271318709</v>
       </c>
       <c r="D53">
-        <v>578.6786216529395</v>
+        <v>570.2237728681291</v>
       </c>
       <c r="E53">
-        <v>9.161000000000058</v>
+        <v>30.37200000000007</v>
       </c>
       <c r="F53">
-        <v>1081.761</v>
+        <v>1102.972</v>
       </c>
       <c r="G53">
         <v>178.9</v>
@@ -5764,37 +5764,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M53">
-        <v>255.0792438</v>
+        <v>260.0807976</v>
       </c>
       <c r="N53">
-        <v>-161.9459104666666</v>
+        <v>-166.9474642666666</v>
       </c>
       <c r="O53">
-        <v>-32.38918209333333</v>
+        <v>-33.38949285333333</v>
       </c>
       <c r="P53">
-        <v>-129.5567283733333</v>
+        <v>-133.5579714133333</v>
       </c>
       <c r="Q53">
-        <v>-43.35672837333334</v>
+        <v>-47.3579714133333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.127481780604813</v>
+        <v>0.1291834843674133</v>
       </c>
       <c r="T53">
-        <v>1.679463380798634</v>
+        <v>1.714452201231939</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.07302305898817578</v>
+        <v>0.07161876939224933</v>
       </c>
       <c r="W53">
-        <v>0.2185811626905882</v>
+        <v>0.2189122941773076</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3651152949408789</v>
+        <v>0.3580938469612467</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1758424654685583</v>
+        <v>0.1777424654685583</v>
       </c>
       <c r="C54">
-        <v>-353.8482271318709</v>
+        <v>-383.2705726194814</v>
       </c>
       <c r="D54">
-        <v>570.2237728681291</v>
+        <v>562.0124273805186</v>
       </c>
       <c r="E54">
-        <v>30.37200000000007</v>
+        <v>51.58300000000008</v>
       </c>
       <c r="F54">
-        <v>1102.972</v>
+        <v>1124.183</v>
       </c>
       <c r="G54">
         <v>178.9</v>
@@ -5846,37 +5846,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M54">
-        <v>260.0807976</v>
+        <v>265.0823514</v>
       </c>
       <c r="N54">
-        <v>-166.9474642666666</v>
+        <v>-171.9490180666666</v>
       </c>
       <c r="O54">
-        <v>-33.38949285333333</v>
+        <v>-34.38980361333333</v>
       </c>
       <c r="P54">
-        <v>-133.5579714133333</v>
+        <v>-137.5592144533333</v>
       </c>
       <c r="Q54">
-        <v>-47.3579714133333</v>
+        <v>-51.35921445333332</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1291834843674133</v>
+        <v>0.1309576010560816</v>
       </c>
       <c r="T54">
-        <v>1.714452201231939</v>
+        <v>1.750929907641129</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07161876939224933</v>
+        <v>0.07026747185654651</v>
       </c>
       <c r="W54">
-        <v>0.2189122941773076</v>
+        <v>0.2192309301362264</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3580938469612467</v>
+        <v>0.3513373592827326</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1777424654685583</v>
+        <v>0.1796424654685584</v>
       </c>
       <c r="C55">
-        <v>-383.2705726194814</v>
+        <v>-412.4597849774555</v>
       </c>
       <c r="D55">
-        <v>562.0124273805186</v>
+        <v>554.0342150225446</v>
       </c>
       <c r="E55">
-        <v>51.58300000000008</v>
+        <v>72.7940000000001</v>
       </c>
       <c r="F55">
-        <v>1124.183</v>
+        <v>1145.394</v>
       </c>
       <c r="G55">
         <v>178.9</v>
@@ -5928,37 +5928,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M55">
-        <v>265.0823514</v>
+        <v>270.0839052</v>
       </c>
       <c r="N55">
-        <v>-171.9490180666666</v>
+        <v>-176.9505718666666</v>
       </c>
       <c r="O55">
-        <v>-34.38980361333333</v>
+        <v>-35.39011437333333</v>
       </c>
       <c r="P55">
-        <v>-137.5592144533333</v>
+        <v>-141.5604574933333</v>
       </c>
       <c r="Q55">
-        <v>-51.35921445333332</v>
+        <v>-55.36045749333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1309576010560816</v>
+        <v>0.132808853252953</v>
       </c>
       <c r="T55">
-        <v>1.750929907641129</v>
+        <v>1.788993601285502</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07026747185654651</v>
+        <v>0.06896622237772157</v>
       </c>
       <c r="W55">
-        <v>0.2192309301362264</v>
+        <v>0.2195377647633333</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3513373592827326</v>
+        <v>0.3448311118886078</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1796424654685584</v>
+        <v>0.1815424654685583</v>
       </c>
       <c r="C56">
-        <v>-412.4597849774555</v>
+        <v>-441.4256537645313</v>
       </c>
       <c r="D56">
-        <v>554.0342150225446</v>
+        <v>546.2793462354688</v>
       </c>
       <c r="E56">
-        <v>72.7940000000001</v>
+        <v>94.00500000000011</v>
       </c>
       <c r="F56">
-        <v>1145.394</v>
+        <v>1166.605</v>
       </c>
       <c r="G56">
         <v>178.9</v>
@@ -6010,37 +6010,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M56">
-        <v>270.0839052</v>
+        <v>275.085459</v>
       </c>
       <c r="N56">
-        <v>-176.9505718666666</v>
+        <v>-181.9521256666667</v>
       </c>
       <c r="O56">
-        <v>-35.39011437333333</v>
+        <v>-36.39042513333333</v>
       </c>
       <c r="P56">
-        <v>-141.5604574933333</v>
+        <v>-145.5617005333333</v>
       </c>
       <c r="Q56">
-        <v>-55.36045749333334</v>
+        <v>-59.36170053333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.132808853252953</v>
+        <v>0.1347423833252409</v>
       </c>
       <c r="T56">
-        <v>1.788993601285502</v>
+        <v>1.828749014647402</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06896622237772157</v>
+        <v>0.06771229106176301</v>
       </c>
       <c r="W56">
-        <v>0.2195377647633333</v>
+        <v>0.2198334417676363</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3448311118886078</v>
+        <v>0.338561455308815</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1815424654685583</v>
+        <v>0.1834424654685584</v>
       </c>
       <c r="C57">
-        <v>-441.4256537645313</v>
+        <v>-470.1774280038919</v>
       </c>
       <c r="D57">
-        <v>546.2793462354688</v>
+        <v>538.7385719961081</v>
       </c>
       <c r="E57">
-        <v>94.00500000000011</v>
+        <v>115.2160000000001</v>
       </c>
       <c r="F57">
-        <v>1166.605</v>
+        <v>1187.816</v>
       </c>
       <c r="G57">
         <v>178.9</v>
@@ -6092,37 +6092,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M57">
-        <v>275.085459</v>
+        <v>280.0870128</v>
       </c>
       <c r="N57">
-        <v>-181.9521256666667</v>
+        <v>-186.9536794666667</v>
       </c>
       <c r="O57">
-        <v>-36.39042513333333</v>
+        <v>-37.39073589333334</v>
       </c>
       <c r="P57">
-        <v>-145.5617005333333</v>
+        <v>-149.5629435733333</v>
       </c>
       <c r="Q57">
-        <v>-59.36170053333333</v>
+        <v>-63.36294357333335</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1347423833252409</v>
+        <v>0.1367638011280872</v>
       </c>
       <c r="T57">
-        <v>1.828749014647402</v>
+        <v>1.870311492253024</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06771229106176301</v>
+        <v>0.06650314300708865</v>
       </c>
       <c r="W57">
-        <v>0.2198334417676363</v>
+        <v>0.2201185588789285</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.338561455308815</v>
+        <v>0.3325157150354433</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1834424654685584</v>
+        <v>0.1853424654685583</v>
       </c>
       <c r="C58">
-        <v>-470.1774280038919</v>
+        <v>-498.723852982629</v>
       </c>
       <c r="D58">
-        <v>538.7385719961081</v>
+        <v>531.4031470173711</v>
       </c>
       <c r="E58">
-        <v>115.2160000000001</v>
+        <v>136.4270000000001</v>
       </c>
       <c r="F58">
-        <v>1187.816</v>
+        <v>1209.027</v>
       </c>
       <c r="G58">
         <v>178.9</v>
@@ -6174,37 +6174,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M58">
-        <v>280.0870128</v>
+        <v>285.0885666</v>
       </c>
       <c r="N58">
-        <v>-186.9536794666667</v>
+        <v>-191.9552332666667</v>
       </c>
       <c r="O58">
-        <v>-37.39073589333334</v>
+        <v>-38.39104665333334</v>
       </c>
       <c r="P58">
-        <v>-149.5629435733333</v>
+        <v>-153.5641866133333</v>
       </c>
       <c r="Q58">
-        <v>-63.36294357333335</v>
+        <v>-67.36418661333335</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1367638011280872</v>
+        <v>0.1388792383636241</v>
       </c>
       <c r="T58">
-        <v>1.870311492253024</v>
+        <v>1.913807108351932</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06650314300708865</v>
+        <v>0.06533642119994675</v>
       </c>
       <c r="W58">
-        <v>0.2201185588789285</v>
+        <v>0.2203936718810525</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3325157150354433</v>
+        <v>0.3266821059997337</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1853424654685583</v>
+        <v>0.1872424654685584</v>
       </c>
       <c r="C59">
-        <v>-498.723852982629</v>
+        <v>-527.0732040852365</v>
       </c>
       <c r="D59">
-        <v>531.4031470173711</v>
+        <v>524.2647959147636</v>
       </c>
       <c r="E59">
-        <v>136.4270000000001</v>
+        <v>157.6380000000001</v>
       </c>
       <c r="F59">
-        <v>1209.027</v>
+        <v>1230.238</v>
       </c>
       <c r="G59">
         <v>178.9</v>
@@ -6256,37 +6256,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M59">
-        <v>285.0885666</v>
+        <v>290.0901204</v>
       </c>
       <c r="N59">
-        <v>-191.9552332666667</v>
+        <v>-196.9567870666667</v>
       </c>
       <c r="O59">
-        <v>-38.39104665333334</v>
+        <v>-39.39135741333334</v>
       </c>
       <c r="P59">
-        <v>-153.5641866133333</v>
+        <v>-157.5654296533334</v>
       </c>
       <c r="Q59">
-        <v>-67.36418661333335</v>
+        <v>-71.36542965333336</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1388792383636241</v>
+        <v>0.1410954107056152</v>
       </c>
       <c r="T59">
-        <v>1.913807108351932</v>
+        <v>1.959373944265073</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06533642119994675</v>
+        <v>0.06420993117925801</v>
       </c>
       <c r="W59">
-        <v>0.2203936718810525</v>
+        <v>0.220659298227931</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3266821059997337</v>
+        <v>0.32104965589629</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1872424654685583</v>
+        <v>0.1891424654685583</v>
       </c>
       <c r="C60">
-        <v>-527.0732040852361</v>
+        <v>-555.2333179363339</v>
       </c>
       <c r="D60">
-        <v>524.2647959147638</v>
+        <v>517.3156820636659</v>
       </c>
       <c r="E60">
-        <v>157.6379999999999</v>
+        <v>178.8489999999999</v>
       </c>
       <c r="F60">
-        <v>1230.238</v>
+        <v>1251.449</v>
       </c>
       <c r="G60">
         <v>178.9</v>
@@ -6338,37 +6338,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M60">
-        <v>290.0901204</v>
+        <v>295.0916742</v>
       </c>
       <c r="N60">
-        <v>-196.9567870666666</v>
+        <v>-201.9583408666666</v>
       </c>
       <c r="O60">
-        <v>-39.39135741333333</v>
+        <v>-40.39166817333333</v>
       </c>
       <c r="P60">
-        <v>-157.5654296533333</v>
+        <v>-161.5666726933333</v>
       </c>
       <c r="Q60">
-        <v>-71.36542965333331</v>
+        <v>-75.36667269333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1410954107056152</v>
+        <v>0.1434196890155082</v>
       </c>
       <c r="T60">
-        <v>1.959373944265073</v>
+        <v>2.007163552661782</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06420993117925802</v>
+        <v>0.06312162726096551</v>
       </c>
       <c r="W60">
-        <v>0.220659298227931</v>
+        <v>0.2209159202918644</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3210496558962901</v>
+        <v>0.3156081363048275</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1891424654685583</v>
+        <v>0.1910424654685584</v>
       </c>
       <c r="C61">
-        <v>-555.2333179363339</v>
+        <v>-583.2116210990149</v>
       </c>
       <c r="D61">
-        <v>517.3156820636659</v>
+        <v>510.5483789009849</v>
       </c>
       <c r="E61">
-        <v>178.8489999999999</v>
+        <v>200.0599999999999</v>
       </c>
       <c r="F61">
-        <v>1251.449</v>
+        <v>1272.66</v>
       </c>
       <c r="G61">
         <v>178.9</v>
@@ -6420,37 +6420,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M61">
-        <v>295.0916742</v>
+        <v>300.093228</v>
       </c>
       <c r="N61">
-        <v>-201.9583408666666</v>
+        <v>-206.9598946666666</v>
       </c>
       <c r="O61">
-        <v>-40.39166817333333</v>
+        <v>-41.39197893333332</v>
       </c>
       <c r="P61">
-        <v>-161.5666726933333</v>
+        <v>-165.5679157333333</v>
       </c>
       <c r="Q61">
-        <v>-75.36667269333333</v>
+        <v>-79.36791573333329</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1434196890155082</v>
+        <v>0.1458601812408959</v>
       </c>
       <c r="T61">
-        <v>2.007163552661782</v>
+        <v>2.057342641478327</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06312162726096551</v>
+        <v>0.06206960013994942</v>
       </c>
       <c r="W61">
-        <v>0.2209159202918644</v>
+        <v>0.2211639882869999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3156081363048275</v>
+        <v>0.3103480006997471</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1910424654685584</v>
+        <v>0.1929424654685583</v>
       </c>
       <c r="C62">
-        <v>-583.2116210990149</v>
+        <v>-611.0151565497624</v>
       </c>
       <c r="D62">
-        <v>510.5483789009849</v>
+        <v>503.9558434502374</v>
       </c>
       <c r="E62">
-        <v>200.0599999999999</v>
+        <v>221.271</v>
       </c>
       <c r="F62">
-        <v>1272.66</v>
+        <v>1293.871</v>
       </c>
       <c r="G62">
         <v>178.9</v>
@@ -6502,37 +6502,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M62">
-        <v>300.093228</v>
+        <v>305.0947818</v>
       </c>
       <c r="N62">
-        <v>-206.9598946666666</v>
+        <v>-211.9614484666666</v>
       </c>
       <c r="O62">
-        <v>-41.39197893333332</v>
+        <v>-42.39228969333332</v>
       </c>
       <c r="P62">
-        <v>-165.5679157333333</v>
+        <v>-169.5691587733333</v>
       </c>
       <c r="Q62">
-        <v>-79.36791573333329</v>
+        <v>-83.36915877333331</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1458601812408959</v>
+        <v>0.1484258269137394</v>
       </c>
       <c r="T62">
-        <v>2.057342641478327</v>
+        <v>2.110095016900848</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06206960013994942</v>
+        <v>0.06105206571142566</v>
       </c>
       <c r="W62">
-        <v>0.2211639882869999</v>
+        <v>0.2214039229052459</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3103480006997471</v>
+        <v>0.3052603285571283</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1929424654685583</v>
+        <v>0.1948424654685583</v>
       </c>
       <c r="C63">
-        <v>-611.0151565497624</v>
+        <v>-638.6506081283459</v>
       </c>
       <c r="D63">
-        <v>503.9558434502374</v>
+        <v>497.531391871654</v>
       </c>
       <c r="E63">
-        <v>221.271</v>
+        <v>242.482</v>
       </c>
       <c r="F63">
-        <v>1293.871</v>
+        <v>1315.082</v>
       </c>
       <c r="G63">
         <v>178.9</v>
@@ -6584,37 +6584,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M63">
-        <v>305.0947818</v>
+        <v>310.0963356</v>
       </c>
       <c r="N63">
-        <v>-211.9614484666666</v>
+        <v>-216.9630022666666</v>
       </c>
       <c r="O63">
-        <v>-42.39228969333332</v>
+        <v>-43.39260045333333</v>
       </c>
       <c r="P63">
-        <v>-169.5691587733333</v>
+        <v>-173.5704018133333</v>
       </c>
       <c r="Q63">
-        <v>-83.36915877333331</v>
+        <v>-87.3704018133333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1484258269137394</v>
+        <v>0.1511265065693642</v>
       </c>
       <c r="T63">
-        <v>2.110095016900848</v>
+        <v>2.165623833135081</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06105206571142566</v>
+        <v>0.06006735497414459</v>
       </c>
       <c r="W63">
-        <v>0.2214039229052459</v>
+        <v>0.2216361176970967</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3052603285571283</v>
+        <v>0.300336774870723</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1948424654685583</v>
+        <v>0.1967424654685583</v>
       </c>
       <c r="C64">
-        <v>-638.6506081283459</v>
+        <v>-666.1243231411271</v>
       </c>
       <c r="D64">
-        <v>497.531391871654</v>
+        <v>491.2686768588728</v>
       </c>
       <c r="E64">
-        <v>242.482</v>
+        <v>263.693</v>
       </c>
       <c r="F64">
-        <v>1315.082</v>
+        <v>1336.293</v>
       </c>
       <c r="G64">
         <v>178.9</v>
@@ -6666,37 +6666,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M64">
-        <v>310.0963356</v>
+        <v>315.0978894</v>
       </c>
       <c r="N64">
-        <v>-216.9630022666666</v>
+        <v>-221.9645560666666</v>
       </c>
       <c r="O64">
-        <v>-43.39260045333333</v>
+        <v>-44.39291121333333</v>
       </c>
       <c r="P64">
-        <v>-173.5704018133333</v>
+        <v>-177.5716448533333</v>
       </c>
       <c r="Q64">
-        <v>-87.3704018133333</v>
+        <v>-91.37164485333332</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1511265065693642</v>
+        <v>0.1539731689090767</v>
       </c>
       <c r="T64">
-        <v>2.165623833135081</v>
+        <v>2.224154207003596</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06006735497414459</v>
+        <v>0.05911390489518992</v>
       </c>
       <c r="W64">
-        <v>0.2216361176970967</v>
+        <v>0.2218609412257142</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.300336774870723</v>
+        <v>0.2955695244759496</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1967424654685583</v>
+        <v>0.1986424654685583</v>
       </c>
       <c r="C65">
-        <v>-666.1243231411271</v>
+        <v>-693.4423332784626</v>
       </c>
       <c r="D65">
-        <v>491.2686768588728</v>
+        <v>485.1616667215373</v>
       </c>
       <c r="E65">
-        <v>263.693</v>
+        <v>284.904</v>
       </c>
       <c r="F65">
-        <v>1336.293</v>
+        <v>1357.504</v>
       </c>
       <c r="G65">
         <v>178.9</v>
@@ -6748,37 +6748,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M65">
-        <v>315.0978894</v>
+        <v>320.0994432</v>
       </c>
       <c r="N65">
-        <v>-221.9645560666666</v>
+        <v>-226.9661098666666</v>
       </c>
       <c r="O65">
-        <v>-44.39291121333333</v>
+        <v>-45.39322197333333</v>
       </c>
       <c r="P65">
-        <v>-177.5716448533333</v>
+        <v>-181.5728878933333</v>
       </c>
       <c r="Q65">
-        <v>-91.37164485333332</v>
+        <v>-95.37288789333331</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1539731689090767</v>
+        <v>0.156977979156551</v>
       </c>
       <c r="T65">
-        <v>2.224154207003596</v>
+        <v>2.285936268309252</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05911390489518992</v>
+        <v>0.05819025013120258</v>
       </c>
       <c r="W65">
-        <v>0.2218609412257142</v>
+        <v>0.2220787390190624</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2955695244759496</v>
+        <v>0.2909512506560129</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1986424654685583</v>
+        <v>0.2005424654685584</v>
       </c>
       <c r="C66">
-        <v>-693.4423332784626</v>
+        <v>-720.6103739911057</v>
       </c>
       <c r="D66">
-        <v>485.1616667215373</v>
+        <v>479.2046260088942</v>
       </c>
       <c r="E66">
-        <v>284.904</v>
+        <v>306.115</v>
       </c>
       <c r="F66">
-        <v>1357.504</v>
+        <v>1378.715</v>
       </c>
       <c r="G66">
         <v>178.9</v>
@@ -6830,37 +6830,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M66">
-        <v>320.0994432</v>
+        <v>325.100997</v>
       </c>
       <c r="N66">
-        <v>-226.9661098666666</v>
+        <v>-231.9676636666667</v>
       </c>
       <c r="O66">
-        <v>-45.39322197333333</v>
+        <v>-46.39353273333333</v>
       </c>
       <c r="P66">
-        <v>-181.5728878933333</v>
+        <v>-185.5741309333333</v>
       </c>
       <c r="Q66">
-        <v>-95.37288789333331</v>
+        <v>-99.37413093333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.156977979156551</v>
+        <v>0.1601544928467382</v>
       </c>
       <c r="T66">
-        <v>2.285936268309252</v>
+        <v>2.351248733118088</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05819025013120258</v>
+        <v>0.05729501551379945</v>
       </c>
       <c r="W66">
-        <v>0.2220787390190624</v>
+        <v>0.2222898353418461</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2909512506560129</v>
+        <v>0.2864750775689973</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2005424654685584</v>
+        <v>0.2024424654685583</v>
       </c>
       <c r="C67">
-        <v>-720.6103739911057</v>
+        <v>-747.6339024564447</v>
       </c>
       <c r="D67">
-        <v>479.2046260088942</v>
+        <v>473.3920975435552</v>
       </c>
       <c r="E67">
-        <v>306.115</v>
+        <v>327.326</v>
       </c>
       <c r="F67">
-        <v>1378.715</v>
+        <v>1399.926</v>
       </c>
       <c r="G67">
         <v>178.9</v>
@@ -6912,37 +6912,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M67">
-        <v>325.100997</v>
+        <v>330.1025508</v>
       </c>
       <c r="N67">
-        <v>-231.9676636666667</v>
+        <v>-236.9692174666667</v>
       </c>
       <c r="O67">
-        <v>-46.39353273333333</v>
+        <v>-47.39384349333334</v>
       </c>
       <c r="P67">
-        <v>-185.5741309333333</v>
+        <v>-189.5753739733333</v>
       </c>
       <c r="Q67">
-        <v>-99.37413093333333</v>
+        <v>-103.3753739733334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1601544928467382</v>
+        <v>0.163517860283407</v>
       </c>
       <c r="T67">
-        <v>2.351248733118088</v>
+        <v>2.420403107621561</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05729501551379945</v>
+        <v>0.05642690921813583</v>
       </c>
       <c r="W67">
-        <v>0.2222898353418461</v>
+        <v>0.2224945348063636</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2864750775689973</v>
+        <v>0.2821345460906791</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2024424654685583</v>
+        <v>0.2043424654685584</v>
       </c>
       <c r="C68">
-        <v>-747.6339024564447</v>
+        <v>-774.5181142528839</v>
       </c>
       <c r="D68">
-        <v>473.3920975435552</v>
+        <v>467.718885747116</v>
       </c>
       <c r="E68">
-        <v>327.326</v>
+        <v>348.537</v>
       </c>
       <c r="F68">
-        <v>1399.926</v>
+        <v>1421.137</v>
       </c>
       <c r="G68">
         <v>178.9</v>
@@ -6994,37 +6994,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M68">
-        <v>330.1025508</v>
+        <v>335.1041046</v>
       </c>
       <c r="N68">
-        <v>-236.9692174666667</v>
+        <v>-241.9707712666667</v>
       </c>
       <c r="O68">
-        <v>-47.39384349333334</v>
+        <v>-48.39415425333334</v>
       </c>
       <c r="P68">
-        <v>-189.5753739733333</v>
+        <v>-193.5766170133333</v>
       </c>
       <c r="Q68">
-        <v>-103.3753739733334</v>
+        <v>-107.3766170133333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.163517860283407</v>
+        <v>0.167085068170783</v>
       </c>
       <c r="T68">
-        <v>2.420403107621561</v>
+        <v>2.493748656337366</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05642690921813583</v>
+        <v>0.05558471654323828</v>
       </c>
       <c r="W68">
-        <v>0.2224945348063636</v>
+        <v>0.2226931238391044</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2821345460906791</v>
+        <v>0.2779235827161913</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2043424654685584</v>
+        <v>0.2062424654685583</v>
       </c>
       <c r="C69">
-        <v>-774.5181142528839</v>
+        <v>-801.2679588494452</v>
       </c>
       <c r="D69">
-        <v>467.718885747116</v>
+        <v>462.1800411505548</v>
       </c>
       <c r="E69">
-        <v>348.537</v>
+        <v>369.748</v>
       </c>
       <c r="F69">
-        <v>1421.137</v>
+        <v>1442.348</v>
       </c>
       <c r="G69">
         <v>178.9</v>
@@ -7076,37 +7076,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M69">
-        <v>335.1041046</v>
+        <v>340.1056584</v>
       </c>
       <c r="N69">
-        <v>-241.9707712666667</v>
+        <v>-246.9723250666666</v>
       </c>
       <c r="O69">
-        <v>-48.39415425333334</v>
+        <v>-49.39446501333333</v>
       </c>
       <c r="P69">
-        <v>-193.5766170133333</v>
+        <v>-197.5778600533333</v>
       </c>
       <c r="Q69">
-        <v>-107.3766170133333</v>
+        <v>-111.3778600533333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.167085068170783</v>
+        <v>0.1708752265511199</v>
       </c>
       <c r="T69">
-        <v>2.493748656337366</v>
+        <v>2.571678301847908</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05558471654323828</v>
+        <v>0.05476729424113184</v>
       </c>
       <c r="W69">
-        <v>0.2226931238391044</v>
+        <v>0.2228858720179411</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2779235827161913</v>
+        <v>0.2738364712056592</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2062424654685583</v>
+        <v>0.2081424654685584</v>
       </c>
       <c r="C70">
-        <v>-801.2679588494452</v>
+        <v>-827.8881540076655</v>
       </c>
       <c r="D70">
-        <v>462.1800411505548</v>
+        <v>456.7708459923344</v>
       </c>
       <c r="E70">
-        <v>369.748</v>
+        <v>390.9590000000001</v>
       </c>
       <c r="F70">
-        <v>1442.348</v>
+        <v>1463.559</v>
       </c>
       <c r="G70">
         <v>178.9</v>
@@ -7158,37 +7158,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M70">
-        <v>340.1056584</v>
+        <v>345.1072122</v>
       </c>
       <c r="N70">
-        <v>-246.9723250666666</v>
+        <v>-251.9738788666666</v>
       </c>
       <c r="O70">
-        <v>-49.39446501333333</v>
+        <v>-50.39477577333333</v>
       </c>
       <c r="P70">
-        <v>-197.5778600533333</v>
+        <v>-201.5791030933333</v>
       </c>
       <c r="Q70">
-        <v>-111.3778600533333</v>
+        <v>-115.3791030933333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1708752265511199</v>
+        <v>0.1749099112785754</v>
       </c>
       <c r="T70">
-        <v>2.571678301847908</v>
+        <v>2.654635666423648</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05476729424113184</v>
+        <v>0.05397356533908645</v>
       </c>
       <c r="W70">
-        <v>0.2228858720179411</v>
+        <v>0.2230730332930434</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2738364712056592</v>
+        <v>0.2698678266954322</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2081424654685584</v>
+        <v>0.2100424654685583</v>
       </c>
       <c r="C71">
-        <v>-827.8881540076655</v>
+        <v>-854.3831991838599</v>
       </c>
       <c r="D71">
-        <v>456.7708459923344</v>
+        <v>451.48680081614</v>
       </c>
       <c r="E71">
-        <v>390.9590000000001</v>
+        <v>412.1700000000001</v>
       </c>
       <c r="F71">
-        <v>1463.559</v>
+        <v>1484.77</v>
       </c>
       <c r="G71">
         <v>178.9</v>
@@ -7240,37 +7240,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M71">
-        <v>345.1072122</v>
+        <v>350.108766</v>
       </c>
       <c r="N71">
-        <v>-251.9738788666666</v>
+        <v>-256.9754326666666</v>
       </c>
       <c r="O71">
-        <v>-50.39477577333333</v>
+        <v>-51.39508653333333</v>
       </c>
       <c r="P71">
-        <v>-201.5791030933333</v>
+        <v>-205.5803461333333</v>
       </c>
       <c r="Q71">
-        <v>-115.3791030933333</v>
+        <v>-119.3803461333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1749099112785754</v>
+        <v>0.1792135749878613</v>
       </c>
       <c r="T71">
-        <v>2.654635666423648</v>
+        <v>2.743123521971103</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05397356533908645</v>
+        <v>0.05320251440567092</v>
       </c>
       <c r="W71">
-        <v>0.2230730332930434</v>
+        <v>0.2232548471031428</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2698678266954322</v>
+        <v>0.2660125720283547</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2100424654685583</v>
+        <v>0.2119424654685584</v>
       </c>
       <c r="C72">
-        <v>-854.3831991838599</v>
+        <v>-880.7573880117819</v>
       </c>
       <c r="D72">
-        <v>451.48680081614</v>
+        <v>446.323611988218</v>
       </c>
       <c r="E72">
-        <v>412.1700000000001</v>
+        <v>433.3810000000001</v>
       </c>
       <c r="F72">
-        <v>1484.77</v>
+        <v>1505.981</v>
       </c>
       <c r="G72">
         <v>178.9</v>
@@ -7322,37 +7322,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M72">
-        <v>350.108766</v>
+        <v>355.1103198</v>
       </c>
       <c r="N72">
-        <v>-256.9754326666666</v>
+        <v>-261.9769864666666</v>
       </c>
       <c r="O72">
-        <v>-51.39508653333333</v>
+        <v>-52.39539729333333</v>
       </c>
       <c r="P72">
-        <v>-205.5803461333333</v>
+        <v>-209.5815891733333</v>
       </c>
       <c r="Q72">
-        <v>-119.3803461333333</v>
+        <v>-123.3815891733333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1792135749878613</v>
+        <v>0.183814043090891</v>
       </c>
       <c r="T72">
-        <v>2.743123521971103</v>
+        <v>2.837713988245969</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05320251440567092</v>
+        <v>0.05245318321685866</v>
       </c>
       <c r="W72">
-        <v>0.2232548471031428</v>
+        <v>0.2234315393974647</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2660125720283547</v>
+        <v>0.2622659160842934</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2119424654685583</v>
+        <v>0.2138424654685583</v>
       </c>
       <c r="C73">
-        <v>-880.7573880117817</v>
+        <v>-907.0148199384563</v>
       </c>
       <c r="D73">
-        <v>446.323611988218</v>
+        <v>441.2771800615435</v>
       </c>
       <c r="E73">
-        <v>433.3809999999999</v>
+        <v>454.5919999999999</v>
       </c>
       <c r="F73">
-        <v>1505.981</v>
+        <v>1527.192</v>
       </c>
       <c r="G73">
         <v>178.9</v>
@@ -7404,37 +7404,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M73">
-        <v>355.1103198</v>
+        <v>360.1118736</v>
       </c>
       <c r="N73">
-        <v>-261.9769864666666</v>
+        <v>-266.9785402666666</v>
       </c>
       <c r="O73">
-        <v>-52.39539729333333</v>
+        <v>-53.39570805333333</v>
       </c>
       <c r="P73">
-        <v>-209.5815891733333</v>
+        <v>-213.5828322133333</v>
       </c>
       <c r="Q73">
-        <v>-123.3815891733333</v>
+        <v>-127.3828322133333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1838140430908909</v>
+        <v>0.1887431160584228</v>
       </c>
       <c r="T73">
-        <v>2.837713988245967</v>
+        <v>2.939060916397609</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05245318321685867</v>
+        <v>0.05172466678329118</v>
       </c>
       <c r="W73">
-        <v>0.2234315393974647</v>
+        <v>0.2236033235725</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2622659160842933</v>
+        <v>0.2586233339164559</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2138424654685583</v>
+        <v>0.2157424654685584</v>
       </c>
       <c r="C74">
-        <v>-907.0148199384563</v>
+        <v>-933.1594110794653</v>
       </c>
       <c r="D74">
-        <v>441.2771800615435</v>
+        <v>436.3435889205346</v>
       </c>
       <c r="E74">
-        <v>454.5919999999999</v>
+        <v>475.8029999999999</v>
       </c>
       <c r="F74">
-        <v>1527.192</v>
+        <v>1548.403</v>
       </c>
       <c r="G74">
         <v>178.9</v>
@@ -7486,37 +7486,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M74">
-        <v>360.1118736</v>
+        <v>365.1134274</v>
       </c>
       <c r="N74">
-        <v>-266.9785402666666</v>
+        <v>-271.9800940666667</v>
       </c>
       <c r="O74">
-        <v>-53.39570805333333</v>
+        <v>-54.39601881333333</v>
       </c>
       <c r="P74">
-        <v>-213.5828322133333</v>
+        <v>-217.5840752533333</v>
       </c>
       <c r="Q74">
-        <v>-127.3828322133333</v>
+        <v>-131.3840752533333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1887431160584228</v>
+        <v>0.1940373055420681</v>
       </c>
       <c r="T74">
-        <v>2.939060916397609</v>
+        <v>3.047915024412335</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05172466678329118</v>
+        <v>0.05101610970406802</v>
       </c>
       <c r="W74">
-        <v>0.2236033235725</v>
+        <v>0.2237704013317808</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2586233339164559</v>
+        <v>0.25508054852034</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2157424654685584</v>
+        <v>0.2176424654685583</v>
       </c>
       <c r="C75">
-        <v>-933.1594110794653</v>
+        <v>-959.1949043540959</v>
       </c>
       <c r="D75">
-        <v>436.3435889205346</v>
+        <v>431.5190956459039</v>
       </c>
       <c r="E75">
-        <v>475.8029999999999</v>
+        <v>497.0139999999999</v>
       </c>
       <c r="F75">
-        <v>1548.403</v>
+        <v>1569.614</v>
       </c>
       <c r="G75">
         <v>178.9</v>
@@ -7568,37 +7568,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M75">
-        <v>365.1134274</v>
+        <v>370.1149812</v>
       </c>
       <c r="N75">
-        <v>-271.9800940666667</v>
+        <v>-276.9816478666667</v>
       </c>
       <c r="O75">
-        <v>-54.39601881333333</v>
+        <v>-55.39632957333333</v>
       </c>
       <c r="P75">
-        <v>-217.5840752533333</v>
+        <v>-221.5853182933333</v>
       </c>
       <c r="Q75">
-        <v>-131.3840752533333</v>
+        <v>-135.3853182933333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1940373055420681</v>
+        <v>0.1997387403706091</v>
       </c>
       <c r="T75">
-        <v>3.047915024412335</v>
+        <v>3.165142525351271</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05101610970406802</v>
+        <v>0.05032670281617521</v>
       </c>
       <c r="W75">
-        <v>0.2237704013317808</v>
+        <v>0.2239329634759459</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.25508054852034</v>
+        <v>0.251633514080876</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2176424654685583</v>
+        <v>0.2195424654685584</v>
       </c>
       <c r="C76">
-        <v>-959.1949043540959</v>
+        <v>-985.1248789554758</v>
       </c>
       <c r="D76">
-        <v>431.5190956459039</v>
+        <v>426.800121044524</v>
       </c>
       <c r="E76">
-        <v>497.0139999999999</v>
+        <v>518.2249999999999</v>
       </c>
       <c r="F76">
-        <v>1569.614</v>
+        <v>1590.825</v>
       </c>
       <c r="G76">
         <v>178.9</v>
@@ -7650,37 +7650,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M76">
-        <v>370.1149812</v>
+        <v>375.116535</v>
       </c>
       <c r="N76">
-        <v>-276.9816478666667</v>
+        <v>-281.9832016666667</v>
       </c>
       <c r="O76">
-        <v>-55.39632957333333</v>
+        <v>-56.39664033333334</v>
       </c>
       <c r="P76">
-        <v>-221.5853182933333</v>
+        <v>-225.5865613333333</v>
       </c>
       <c r="Q76">
-        <v>-135.3853182933333</v>
+        <v>-139.3865613333334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1997387403706091</v>
+        <v>0.2058962899854335</v>
       </c>
       <c r="T76">
-        <v>3.165142525351271</v>
+        <v>3.291748226365323</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05032670281617521</v>
+        <v>0.04965568011195953</v>
       </c>
       <c r="W76">
-        <v>0.2239329634759459</v>
+        <v>0.2240911906296</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.251633514080876</v>
+        <v>0.2482784005597976</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2195424654685584</v>
+        <v>0.2214424654685583</v>
       </c>
       <c r="C77">
-        <v>-985.1248789554758</v>
+        <v>-1010.952759206054</v>
       </c>
       <c r="D77">
-        <v>426.800121044524</v>
+        <v>422.1832407939463</v>
       </c>
       <c r="E77">
-        <v>518.2249999999999</v>
+        <v>539.4360000000001</v>
       </c>
       <c r="F77">
-        <v>1590.825</v>
+        <v>1612.036</v>
       </c>
       <c r="G77">
         <v>178.9</v>
@@ -7732,37 +7732,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M77">
-        <v>375.116535</v>
+        <v>380.1180888</v>
       </c>
       <c r="N77">
-        <v>-281.9832016666667</v>
+        <v>-286.9847554666667</v>
       </c>
       <c r="O77">
-        <v>-56.39664033333334</v>
+        <v>-57.39695109333334</v>
       </c>
       <c r="P77">
-        <v>-225.5865613333333</v>
+        <v>-229.5878043733333</v>
       </c>
       <c r="Q77">
-        <v>-139.3865613333334</v>
+        <v>-143.3878043733334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2058962899854335</v>
+        <v>0.2125669687348266</v>
       </c>
       <c r="T77">
-        <v>3.291748226365323</v>
+        <v>3.428904402463878</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04965568011195953</v>
+        <v>0.04900231589996006</v>
       </c>
       <c r="W77">
-        <v>0.2240911906296</v>
+        <v>0.2242452539107894</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2482784005597976</v>
+        <v>0.2450115794998002</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2214424654685583</v>
+        <v>0.2233424654685583</v>
       </c>
       <c r="C78">
-        <v>-1010.952759206054</v>
+        <v>-1036.681822844471</v>
       </c>
       <c r="D78">
-        <v>422.1832407939463</v>
+        <v>417.6651771555286</v>
       </c>
       <c r="E78">
-        <v>539.4360000000001</v>
+        <v>560.6470000000002</v>
       </c>
       <c r="F78">
-        <v>1612.036</v>
+        <v>1633.247</v>
       </c>
       <c r="G78">
         <v>178.9</v>
@@ -7814,37 +7814,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M78">
-        <v>380.1180888</v>
+        <v>385.1196426</v>
       </c>
       <c r="N78">
-        <v>-286.9847554666667</v>
+        <v>-291.9863092666667</v>
       </c>
       <c r="O78">
-        <v>-57.39695109333334</v>
+        <v>-58.39726185333334</v>
       </c>
       <c r="P78">
-        <v>-229.5878043733333</v>
+        <v>-233.5890474133334</v>
       </c>
       <c r="Q78">
-        <v>-143.3878043733334</v>
+        <v>-147.3890474133334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2125669687348266</v>
+        <v>0.219817706505906</v>
       </c>
       <c r="T78">
-        <v>3.428904402463878</v>
+        <v>3.577987202571003</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04900231589996006</v>
+        <v>0.04836592218697357</v>
       </c>
       <c r="W78">
-        <v>0.2242452539107894</v>
+        <v>0.2243953155483117</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2450115794998002</v>
+        <v>0.2418296109348678</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2233424654685583</v>
+        <v>0.2252424654685583</v>
       </c>
       <c r="C79">
-        <v>-1036.681822844471</v>
+        <v>-1062.315208785967</v>
       </c>
       <c r="D79">
-        <v>417.6651771555286</v>
+        <v>413.2427912140329</v>
       </c>
       <c r="E79">
-        <v>560.6470000000002</v>
+        <v>581.8580000000002</v>
       </c>
       <c r="F79">
-        <v>1633.247</v>
+        <v>1654.458</v>
       </c>
       <c r="G79">
         <v>178.9</v>
@@ -7896,37 +7896,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M79">
-        <v>385.1196426</v>
+        <v>390.1211964</v>
       </c>
       <c r="N79">
-        <v>-291.9863092666667</v>
+        <v>-296.9878630666667</v>
       </c>
       <c r="O79">
-        <v>-58.39726185333334</v>
+        <v>-59.39757261333335</v>
       </c>
       <c r="P79">
-        <v>-233.5890474133334</v>
+        <v>-237.5902904533334</v>
       </c>
       <c r="Q79">
-        <v>-147.3890474133334</v>
+        <v>-151.3902904533334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.219817706505906</v>
+        <v>0.2277276022561744</v>
       </c>
       <c r="T79">
-        <v>3.577987202571003</v>
+        <v>3.740622984506048</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04836592218697357</v>
+        <v>0.04774584626149955</v>
       </c>
       <c r="W79">
-        <v>0.2243953155483117</v>
+        <v>0.2245415294515384</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2418296109348678</v>
+        <v>0.2387292313074977</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2252424654685583</v>
+        <v>0.2271424654685583</v>
       </c>
       <c r="C80">
-        <v>-1062.315208785967</v>
+        <v>-1087.855924394928</v>
       </c>
       <c r="D80">
-        <v>413.2427912140329</v>
+        <v>408.913075605072</v>
       </c>
       <c r="E80">
-        <v>581.8580000000002</v>
+        <v>603.0690000000002</v>
       </c>
       <c r="F80">
-        <v>1654.458</v>
+        <v>1675.669</v>
       </c>
       <c r="G80">
         <v>178.9</v>
@@ -7978,37 +7978,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M80">
-        <v>390.1211964</v>
+        <v>395.1227502</v>
       </c>
       <c r="N80">
-        <v>-296.9878630666667</v>
+        <v>-301.9894168666667</v>
       </c>
       <c r="O80">
-        <v>-59.39757261333335</v>
+        <v>-60.39788337333334</v>
       </c>
       <c r="P80">
-        <v>-237.5902904533334</v>
+        <v>-241.5915334933334</v>
       </c>
       <c r="Q80">
-        <v>-151.3902904533334</v>
+        <v>-155.3915334933334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2277276022561744</v>
+        <v>0.2363908214112304</v>
       </c>
       <c r="T80">
-        <v>3.740622984506048</v>
+        <v>3.918747888530147</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04774584626149955</v>
+        <v>0.04714146846072107</v>
       </c>
       <c r="W80">
-        <v>0.2245415294515384</v>
+        <v>0.224684041736962</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2387292313074977</v>
+        <v>0.2357073423036052</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2271424654685583</v>
+        <v>0.2290424654685583</v>
       </c>
       <c r="C81">
-        <v>-1087.855924394928</v>
+        <v>-1113.306852304995</v>
       </c>
       <c r="D81">
-        <v>408.913075605072</v>
+        <v>404.673147695005</v>
       </c>
       <c r="E81">
-        <v>603.0690000000002</v>
+        <v>624.2800000000002</v>
       </c>
       <c r="F81">
-        <v>1675.669</v>
+        <v>1696.88</v>
       </c>
       <c r="G81">
         <v>178.9</v>
@@ -8060,37 +8060,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M81">
-        <v>395.1227502</v>
+        <v>400.1243040000001</v>
       </c>
       <c r="N81">
-        <v>-301.9894168666667</v>
+        <v>-306.9909706666667</v>
       </c>
       <c r="O81">
-        <v>-60.39788337333334</v>
+        <v>-61.39819413333335</v>
       </c>
       <c r="P81">
-        <v>-241.5915334933334</v>
+        <v>-245.5927765333334</v>
       </c>
       <c r="Q81">
-        <v>-155.3915334933334</v>
+        <v>-159.3927765333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2363908214112304</v>
+        <v>0.2459203624817919</v>
       </c>
       <c r="T81">
-        <v>3.918747888530147</v>
+        <v>4.114685282956653</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04714146846072107</v>
+        <v>0.04655220010496205</v>
       </c>
       <c r="W81">
-        <v>0.224684041736962</v>
+        <v>0.22482299121525</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2357073423036052</v>
+        <v>0.2327610005248102</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2290424654685583</v>
+        <v>0.2309424654685584</v>
       </c>
       <c r="C82">
-        <v>-1113.306852304995</v>
+        <v>-1138.670756819228</v>
       </c>
       <c r="D82">
-        <v>404.673147695005</v>
+        <v>400.5202431807722</v>
       </c>
       <c r="E82">
-        <v>624.2800000000002</v>
+        <v>645.4910000000002</v>
       </c>
       <c r="F82">
-        <v>1696.88</v>
+        <v>1718.091</v>
       </c>
       <c r="G82">
         <v>178.9</v>
@@ -8142,37 +8142,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M82">
-        <v>400.1243040000001</v>
+        <v>405.1258578000001</v>
       </c>
       <c r="N82">
-        <v>-306.9909706666667</v>
+        <v>-311.9925244666667</v>
       </c>
       <c r="O82">
-        <v>-61.39819413333335</v>
+        <v>-62.39850489333335</v>
       </c>
       <c r="P82">
-        <v>-245.5927765333334</v>
+        <v>-249.5940195733334</v>
       </c>
       <c r="Q82">
-        <v>-159.3927765333334</v>
+        <v>-163.3940195733334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2459203624817919</v>
+        <v>0.2564530131387284</v>
       </c>
       <c r="T82">
-        <v>4.114685282956653</v>
+        <v>4.331247666270163</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04655220010496205</v>
+        <v>0.04597748158514771</v>
       </c>
       <c r="W82">
-        <v>0.22482299121525</v>
+        <v>0.2249585098422222</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2327610005248102</v>
+        <v>0.2298874079257385</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2309424654685584</v>
+        <v>0.2328424654685583</v>
       </c>
       <c r="C83">
-        <v>-1138.670756819228</v>
+        <v>-1163.950289920185</v>
       </c>
       <c r="D83">
-        <v>400.5202431807722</v>
+        <v>396.4517100798152</v>
       </c>
       <c r="E83">
-        <v>645.4910000000002</v>
+        <v>666.7020000000002</v>
       </c>
       <c r="F83">
-        <v>1718.091</v>
+        <v>1739.302</v>
       </c>
       <c r="G83">
         <v>178.9</v>
@@ -8224,37 +8224,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M83">
-        <v>405.1258578000001</v>
+        <v>410.1274116000001</v>
       </c>
       <c r="N83">
-        <v>-311.9925244666667</v>
+        <v>-316.9940782666667</v>
       </c>
       <c r="O83">
-        <v>-62.39850489333335</v>
+        <v>-63.39881565333335</v>
       </c>
       <c r="P83">
-        <v>-249.5940195733334</v>
+        <v>-253.5952626133334</v>
       </c>
       <c r="Q83">
-        <v>-163.3940195733334</v>
+        <v>-167.3952626133334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2564530131387284</v>
+        <v>0.2681559583131021</v>
       </c>
       <c r="T83">
-        <v>4.331247666270163</v>
+        <v>4.571872536618504</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04597748158514771</v>
+        <v>0.04541678059020688</v>
       </c>
       <c r="W83">
-        <v>0.2249585098422222</v>
+        <v>0.2250907231368292</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2298874079257385</v>
+        <v>0.2270839029510343</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2328424654685583</v>
+        <v>0.2347424654685583</v>
       </c>
       <c r="C84">
-        <v>-1163.950289920185</v>
+        <v>-1189.147996917384</v>
       </c>
       <c r="D84">
-        <v>396.4517100798152</v>
+        <v>392.4650030826156</v>
       </c>
       <c r="E84">
-        <v>666.7020000000002</v>
+        <v>687.9130000000002</v>
       </c>
       <c r="F84">
-        <v>1739.302</v>
+        <v>1760.513</v>
       </c>
       <c r="G84">
         <v>178.9</v>
@@ -8306,37 +8306,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M84">
-        <v>410.1274116000001</v>
+        <v>415.1289654</v>
       </c>
       <c r="N84">
-        <v>-316.9940782666667</v>
+        <v>-321.9956320666666</v>
       </c>
       <c r="O84">
-        <v>-63.39881565333335</v>
+        <v>-64.39912641333333</v>
       </c>
       <c r="P84">
-        <v>-253.5952626133334</v>
+        <v>-257.5965056533333</v>
       </c>
       <c r="Q84">
-        <v>-167.3952626133334</v>
+        <v>-171.3965056533333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2681559583131021</v>
+        <v>0.2812357205668141</v>
       </c>
       <c r="T84">
-        <v>4.571872536618504</v>
+        <v>4.840806215243123</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04541678059020688</v>
+        <v>0.04486959046261403</v>
       </c>
       <c r="W84">
-        <v>0.2250907231368292</v>
+        <v>0.2252197505689156</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2270839029510343</v>
+        <v>0.2243479523130703</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2347424654685583</v>
+        <v>0.2366424654685584</v>
       </c>
       <c r="C85">
-        <v>-1189.147996917384</v>
+        <v>-1214.26632175741</v>
       </c>
       <c r="D85">
-        <v>392.4650030826156</v>
+        <v>388.5576782425904</v>
       </c>
       <c r="E85">
-        <v>687.9130000000002</v>
+        <v>709.1240000000003</v>
       </c>
       <c r="F85">
-        <v>1760.513</v>
+        <v>1781.724</v>
       </c>
       <c r="G85">
         <v>178.9</v>
@@ -8388,37 +8388,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M85">
-        <v>415.1289654</v>
+        <v>420.1305192</v>
       </c>
       <c r="N85">
-        <v>-321.9956320666666</v>
+        <v>-326.9971858666667</v>
       </c>
       <c r="O85">
-        <v>-64.39912641333333</v>
+        <v>-65.39943717333334</v>
       </c>
       <c r="P85">
-        <v>-257.5965056533333</v>
+        <v>-261.5977486933333</v>
       </c>
       <c r="Q85">
-        <v>-171.3965056533333</v>
+        <v>-175.3977486933333</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2812357205668141</v>
+        <v>0.29595045310224</v>
       </c>
       <c r="T85">
-        <v>4.840806215243123</v>
+        <v>5.143356603695819</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04486959046261403</v>
+        <v>0.04433542867139244</v>
       </c>
       <c r="W85">
-        <v>0.2252197505689156</v>
+        <v>0.2253457059192857</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2243479523130703</v>
+        <v>0.2216771433569622</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2366424654685583</v>
+        <v>0.2385424654685583</v>
       </c>
       <c r="C86">
-        <v>-1214.26632175741</v>
+        <v>-1239.307612019943</v>
       </c>
       <c r="D86">
-        <v>388.5576782425904</v>
+        <v>384.7273879800567</v>
       </c>
       <c r="E86">
-        <v>709.124</v>
+        <v>730.335</v>
       </c>
       <c r="F86">
-        <v>1781.724</v>
+        <v>1802.935</v>
       </c>
       <c r="G86">
         <v>178.9</v>
@@ -8470,37 +8470,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M86">
-        <v>420.1305192</v>
+        <v>425.132073</v>
       </c>
       <c r="N86">
-        <v>-326.9971858666667</v>
+        <v>-331.9987396666667</v>
       </c>
       <c r="O86">
-        <v>-65.39943717333334</v>
+        <v>-66.39974793333333</v>
       </c>
       <c r="P86">
-        <v>-261.5977486933333</v>
+        <v>-265.5989917333333</v>
       </c>
       <c r="Q86">
-        <v>-175.3977486933333</v>
+        <v>-179.3989917333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2959504531022398</v>
+        <v>0.3126271499757225</v>
       </c>
       <c r="T86">
-        <v>5.143356603695816</v>
+        <v>5.486247043942203</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04433542867139244</v>
+        <v>0.04381383539290547</v>
       </c>
       <c r="W86">
-        <v>0.2253457059192857</v>
+        <v>0.2254686976143529</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2216771433569621</v>
+        <v>0.2190691769645273</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2385424654685583</v>
+        <v>0.2404424654685584</v>
       </c>
       <c r="C87">
-        <v>-1239.307612019943</v>
+        <v>-1264.274123621188</v>
       </c>
       <c r="D87">
-        <v>384.7273879800567</v>
+        <v>380.9718763788117</v>
       </c>
       <c r="E87">
-        <v>730.335</v>
+        <v>751.546</v>
       </c>
       <c r="F87">
-        <v>1802.935</v>
+        <v>1824.146</v>
       </c>
       <c r="G87">
         <v>178.9</v>
@@ -8552,37 +8552,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M87">
-        <v>425.132073</v>
+        <v>430.1336268</v>
       </c>
       <c r="N87">
-        <v>-331.9987396666667</v>
+        <v>-337.0002934666667</v>
       </c>
       <c r="O87">
-        <v>-66.39974793333333</v>
+        <v>-67.40005869333334</v>
       </c>
       <c r="P87">
-        <v>-265.5989917333333</v>
+        <v>-269.6002347733333</v>
       </c>
       <c r="Q87">
-        <v>-179.3989917333333</v>
+        <v>-183.4002347733334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3126271499757225</v>
+        <v>0.3316862321168456</v>
       </c>
       <c r="T87">
-        <v>5.486247043942203</v>
+        <v>5.878121832795219</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04381383539290547</v>
+        <v>0.04330437219066238</v>
       </c>
       <c r="W87">
-        <v>0.2254686976143529</v>
+        <v>0.2255888290374418</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2190691769645273</v>
+        <v>0.2165218609533118</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2404424654685584</v>
+        <v>0.2423424654685583</v>
       </c>
       <c r="C88">
-        <v>-1264.274123621188</v>
+        <v>-1289.168025244479</v>
       </c>
       <c r="D88">
-        <v>380.9718763788117</v>
+        <v>377.2889747555209</v>
       </c>
       <c r="E88">
-        <v>751.546</v>
+        <v>772.7570000000001</v>
       </c>
       <c r="F88">
-        <v>1824.146</v>
+        <v>1845.357</v>
       </c>
       <c r="G88">
         <v>178.9</v>
@@ -8634,37 +8634,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M88">
-        <v>430.1336268</v>
+        <v>435.1351806</v>
       </c>
       <c r="N88">
-        <v>-337.0002934666667</v>
+        <v>-342.0018472666667</v>
       </c>
       <c r="O88">
-        <v>-67.40005869333334</v>
+        <v>-68.40036945333334</v>
       </c>
       <c r="P88">
-        <v>-269.6002347733333</v>
+        <v>-273.6014778133334</v>
       </c>
       <c r="Q88">
-        <v>-183.4002347733334</v>
+        <v>-187.4014778133334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3316862321168456</v>
+        <v>0.3536774807412182</v>
       </c>
       <c r="T88">
-        <v>5.878121832795219</v>
+        <v>6.330285050702543</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04330437219066238</v>
+        <v>0.04280662078617201</v>
       </c>
       <c r="W88">
-        <v>0.2255888290374418</v>
+        <v>0.2257061988186206</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2165218609533118</v>
+        <v>0.2140331039308599</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2423424654685583</v>
+        <v>0.2442424654685583</v>
       </c>
       <c r="C89">
-        <v>-1289.168025244479</v>
+        <v>-1313.991402516364</v>
       </c>
       <c r="D89">
-        <v>377.2889747555209</v>
+        <v>373.6765974836356</v>
       </c>
       <c r="E89">
-        <v>772.7570000000001</v>
+        <v>793.9680000000001</v>
       </c>
       <c r="F89">
-        <v>1845.357</v>
+        <v>1866.568</v>
       </c>
       <c r="G89">
         <v>178.9</v>
@@ -8716,37 +8716,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M89">
-        <v>435.1351806</v>
+        <v>440.1367344</v>
       </c>
       <c r="N89">
-        <v>-342.0018472666667</v>
+        <v>-347.0034010666667</v>
       </c>
       <c r="O89">
-        <v>-68.40036945333334</v>
+        <v>-69.40068021333335</v>
       </c>
       <c r="P89">
-        <v>-273.6014778133334</v>
+        <v>-277.6027208533334</v>
       </c>
       <c r="Q89">
-        <v>-187.4014778133334</v>
+        <v>-191.4027208533334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3536774807412182</v>
+        <v>0.3793339374696532</v>
       </c>
       <c r="T89">
-        <v>6.330285050702543</v>
+        <v>6.857808804927755</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04280662078617201</v>
+        <v>0.04232018191360187</v>
       </c>
       <c r="W89">
-        <v>0.2257061988186206</v>
+        <v>0.2258209011047727</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2140331039308599</v>
+        <v>0.2116009095680093</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2442424654685583</v>
+        <v>0.2461424654685583</v>
       </c>
       <c r="C90">
-        <v>-1313.991402516364</v>
+        <v>-1338.74626194506</v>
       </c>
       <c r="D90">
-        <v>373.6765974836356</v>
+        <v>370.1327380549399</v>
       </c>
       <c r="E90">
-        <v>793.9680000000001</v>
+        <v>815.1790000000001</v>
       </c>
       <c r="F90">
-        <v>1866.568</v>
+        <v>1887.779</v>
       </c>
       <c r="G90">
         <v>178.9</v>
@@ -8798,37 +8798,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M90">
-        <v>440.1367344</v>
+        <v>445.1382882</v>
       </c>
       <c r="N90">
-        <v>-347.0034010666667</v>
+        <v>-352.0049548666667</v>
       </c>
       <c r="O90">
-        <v>-69.40068021333335</v>
+        <v>-70.40099097333335</v>
       </c>
       <c r="P90">
-        <v>-277.6027208533334</v>
+        <v>-281.6039638933333</v>
       </c>
       <c r="Q90">
-        <v>-191.4027208533334</v>
+        <v>-195.4039638933334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3793339374696532</v>
+        <v>0.4096552045123489</v>
       </c>
       <c r="T90">
-        <v>6.857808804927755</v>
+        <v>7.481245969012097</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04232018191360187</v>
+        <v>0.04184467425165129</v>
       </c>
       <c r="W90">
-        <v>0.2258209011047727</v>
+        <v>0.2259330258114606</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2116009095680093</v>
+        <v>0.2092233712582564</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2461424654685583</v>
+        <v>0.2480424654685583</v>
       </c>
       <c r="C91">
-        <v>-1338.74626194506</v>
+        <v>-1363.434534636901</v>
       </c>
       <c r="D91">
-        <v>370.1327380549399</v>
+        <v>366.6554653630991</v>
       </c>
       <c r="E91">
-        <v>815.1790000000001</v>
+        <v>836.3900000000001</v>
       </c>
       <c r="F91">
-        <v>1887.779</v>
+        <v>1908.99</v>
       </c>
       <c r="G91">
         <v>178.9</v>
@@ -8880,37 +8880,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M91">
-        <v>445.1382882</v>
+        <v>450.139842</v>
       </c>
       <c r="N91">
-        <v>-352.0049548666667</v>
+        <v>-357.0065086666667</v>
       </c>
       <c r="O91">
-        <v>-70.40099097333335</v>
+        <v>-71.40130173333334</v>
       </c>
       <c r="P91">
-        <v>-281.6039638933333</v>
+        <v>-285.6052069333334</v>
       </c>
       <c r="Q91">
-        <v>-195.4039638933334</v>
+        <v>-199.4052069333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4096552045123489</v>
+        <v>0.4460407249635838</v>
       </c>
       <c r="T91">
-        <v>7.481245969012097</v>
+        <v>8.229370565913307</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04184467425165129</v>
+        <v>0.04137973342663294</v>
       </c>
       <c r="W91">
-        <v>0.2259330258114606</v>
+        <v>0.226042658858</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2092233712582564</v>
+        <v>0.2068986671331646</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2480424654685583</v>
+        <v>0.2499424654685584</v>
       </c>
       <c r="C92">
-        <v>-1363.434534636901</v>
+        <v>-1388.058079805252</v>
       </c>
       <c r="D92">
-        <v>366.6554653630991</v>
+        <v>363.2429201947486</v>
       </c>
       <c r="E92">
-        <v>836.3900000000001</v>
+        <v>857.6010000000001</v>
       </c>
       <c r="F92">
-        <v>1908.99</v>
+        <v>1930.201</v>
       </c>
       <c r="G92">
         <v>178.9</v>
@@ -8962,37 +8962,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M92">
-        <v>450.139842</v>
+        <v>455.1413958</v>
       </c>
       <c r="N92">
-        <v>-357.0065086666667</v>
+        <v>-362.0080624666666</v>
       </c>
       <c r="O92">
-        <v>-71.40130173333334</v>
+        <v>-72.40161249333333</v>
       </c>
       <c r="P92">
-        <v>-285.6052069333334</v>
+        <v>-289.6064499733333</v>
       </c>
       <c r="Q92">
-        <v>-199.4052069333334</v>
+        <v>-203.4064499733333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4460407249635838</v>
+        <v>0.4905119166262044</v>
       </c>
       <c r="T92">
-        <v>8.229370565913307</v>
+        <v>9.14374507323701</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04137973342663294</v>
+        <v>0.04092501108128533</v>
       </c>
       <c r="W92">
-        <v>0.226042658858</v>
+        <v>0.2261498823870329</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2068986671331646</v>
+        <v>0.2046250554064267</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2499424654685584</v>
+        <v>0.2518424654685584</v>
       </c>
       <c r="C93">
-        <v>-1388.058079805252</v>
+        <v>-1412.618688085275</v>
       </c>
       <c r="D93">
-        <v>363.2429201947486</v>
+        <v>359.8933119147247</v>
       </c>
       <c r="E93">
-        <v>857.6010000000001</v>
+        <v>878.8120000000001</v>
       </c>
       <c r="F93">
-        <v>1930.201</v>
+        <v>1951.412</v>
       </c>
       <c r="G93">
         <v>178.9</v>
@@ -9044,37 +9044,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M93">
-        <v>455.1413958</v>
+        <v>460.1429496</v>
       </c>
       <c r="N93">
-        <v>-362.0080624666666</v>
+        <v>-367.0096162666666</v>
       </c>
       <c r="O93">
-        <v>-72.40161249333333</v>
+        <v>-73.40192325333332</v>
       </c>
       <c r="P93">
-        <v>-289.6064499733333</v>
+        <v>-293.6076930133333</v>
       </c>
       <c r="Q93">
-        <v>-203.4064499733333</v>
+        <v>-207.4076930133333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4905119166262044</v>
+        <v>0.5461009062044799</v>
       </c>
       <c r="T93">
-        <v>9.14374507323701</v>
+        <v>10.28671320739164</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04092501108128533</v>
+        <v>0.04048017400431483</v>
       </c>
       <c r="W93">
-        <v>0.2261498823870329</v>
+        <v>0.2262547749697826</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2046250554064267</v>
+        <v>0.2024008700215743</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2518424654685584</v>
+        <v>0.2537424654685583</v>
       </c>
       <c r="C94">
-        <v>-1412.618688085275</v>
+        <v>-1437.118084666979</v>
       </c>
       <c r="D94">
-        <v>359.8933119147247</v>
+        <v>356.6049153330204</v>
       </c>
       <c r="E94">
-        <v>878.8120000000001</v>
+        <v>900.0230000000001</v>
       </c>
       <c r="F94">
-        <v>1951.412</v>
+        <v>1972.623</v>
       </c>
       <c r="G94">
         <v>178.9</v>
@@ -9126,37 +9126,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M94">
-        <v>460.1429496</v>
+        <v>465.1445034</v>
       </c>
       <c r="N94">
-        <v>-367.0096162666666</v>
+        <v>-372.0111700666666</v>
       </c>
       <c r="O94">
-        <v>-73.40192325333332</v>
+        <v>-74.40223401333333</v>
       </c>
       <c r="P94">
-        <v>-293.6076930133333</v>
+        <v>-297.6089360533333</v>
       </c>
       <c r="Q94">
-        <v>-207.4076930133333</v>
+        <v>-211.4089360533333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5461009062044799</v>
+        <v>0.6175724642336915</v>
       </c>
       <c r="T94">
-        <v>10.28671320739164</v>
+        <v>11.75624366559045</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04048017400431483</v>
+        <v>0.04004490331609639</v>
       </c>
       <c r="W94">
-        <v>0.2262547749697826</v>
+        <v>0.2263574117980645</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2024008700215743</v>
+        <v>0.200224516580482</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2537424654685583</v>
+        <v>0.2556424654685584</v>
       </c>
       <c r="C95">
-        <v>-1437.118084666979</v>
+        <v>-1461.557932258052</v>
       </c>
       <c r="D95">
-        <v>356.6049153330204</v>
+        <v>353.3760677419484</v>
       </c>
       <c r="E95">
-        <v>900.0230000000001</v>
+        <v>921.2340000000002</v>
       </c>
       <c r="F95">
-        <v>1972.623</v>
+        <v>1993.834</v>
       </c>
       <c r="G95">
         <v>178.9</v>
@@ -9208,37 +9208,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M95">
-        <v>465.1445034</v>
+        <v>470.1460572</v>
       </c>
       <c r="N95">
-        <v>-372.0111700666666</v>
+        <v>-377.0127238666666</v>
       </c>
       <c r="O95">
-        <v>-74.40223401333333</v>
+        <v>-75.40254477333333</v>
       </c>
       <c r="P95">
-        <v>-297.6089360533333</v>
+        <v>-301.6101790933333</v>
       </c>
       <c r="Q95">
-        <v>-211.4089360533333</v>
+        <v>-215.4101790933333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6175724642336915</v>
+        <v>0.7128678749393068</v>
       </c>
       <c r="T95">
-        <v>11.75624366559045</v>
+        <v>13.71561760985552</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04004490331609639</v>
+        <v>0.03961889370635069</v>
       </c>
       <c r="W95">
-        <v>0.2263574117980645</v>
+        <v>0.2264578648640425</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.200224516580482</v>
+        <v>0.1980944685317535</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2556424654685584</v>
+        <v>0.2575424654685584</v>
       </c>
       <c r="C96">
-        <v>-1461.557932258052</v>
+        <v>-1485.939833887179</v>
       </c>
       <c r="D96">
-        <v>353.3760677419484</v>
+        <v>350.205166112821</v>
       </c>
       <c r="E96">
-        <v>921.2340000000002</v>
+        <v>942.4450000000002</v>
       </c>
       <c r="F96">
-        <v>1993.834</v>
+        <v>2015.045</v>
       </c>
       <c r="G96">
         <v>178.9</v>
@@ -9290,37 +9290,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M96">
-        <v>470.1460572</v>
+        <v>475.147611</v>
       </c>
       <c r="N96">
-        <v>-377.0127238666666</v>
+        <v>-382.0142776666667</v>
       </c>
       <c r="O96">
-        <v>-75.40254477333333</v>
+        <v>-76.40285553333334</v>
       </c>
       <c r="P96">
-        <v>-301.6101790933333</v>
+        <v>-305.6114221333333</v>
       </c>
       <c r="Q96">
-        <v>-215.4101790933333</v>
+        <v>-219.4114221333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7128678749393068</v>
+        <v>0.8462814499271686</v>
       </c>
       <c r="T96">
-        <v>13.71561760985552</v>
+        <v>16.45874113182663</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03961889370635069</v>
+        <v>0.03920185271996805</v>
       </c>
       <c r="W96">
-        <v>0.2264578648640425</v>
+        <v>0.2265562031286316</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1980944685317535</v>
+        <v>0.1960092635998403</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2575424654685584</v>
+        <v>0.2594424654685584</v>
       </c>
       <c r="C97">
-        <v>-1485.939833887179</v>
+        <v>-1510.265335557786</v>
       </c>
       <c r="D97">
-        <v>350.205166112821</v>
+        <v>347.0906644422143</v>
       </c>
       <c r="E97">
-        <v>942.4450000000002</v>
+        <v>963.6560000000002</v>
       </c>
       <c r="F97">
-        <v>2015.045</v>
+        <v>2036.256</v>
       </c>
       <c r="G97">
         <v>178.9</v>
@@ -9372,37 +9372,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M97">
-        <v>475.147611</v>
+        <v>480.1491648000001</v>
       </c>
       <c r="N97">
-        <v>-382.0142776666667</v>
+        <v>-387.0158314666667</v>
       </c>
       <c r="O97">
-        <v>-76.40285553333334</v>
+        <v>-77.40316629333334</v>
       </c>
       <c r="P97">
-        <v>-305.6114221333333</v>
+        <v>-309.6126651733333</v>
       </c>
       <c r="Q97">
-        <v>-219.4114221333334</v>
+        <v>-223.4126651733333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8462814499271686</v>
+        <v>1.046401812408961</v>
       </c>
       <c r="T97">
-        <v>16.45874113182663</v>
+        <v>20.5734264147833</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03920185271996805</v>
+        <v>0.03879350008746838</v>
       </c>
       <c r="W97">
-        <v>0.2265562031286316</v>
+        <v>0.226652492679375</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1960092635998403</v>
+        <v>0.1939675004373419</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2594424654685583</v>
+        <v>0.2613424654685584</v>
       </c>
       <c r="C98">
-        <v>-1510.265335557785</v>
+        <v>-1534.535928761411</v>
       </c>
       <c r="D98">
-        <v>347.0906644422143</v>
+        <v>344.031071238589</v>
       </c>
       <c r="E98">
-        <v>963.6559999999999</v>
+        <v>984.8669999999997</v>
       </c>
       <c r="F98">
-        <v>2036.256</v>
+        <v>2057.467</v>
       </c>
       <c r="G98">
         <v>178.9</v>
@@ -9454,37 +9454,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M98">
-        <v>480.1491648</v>
+        <v>485.1507185999999</v>
       </c>
       <c r="N98">
-        <v>-387.0158314666667</v>
+        <v>-392.0173852666666</v>
       </c>
       <c r="O98">
-        <v>-77.40316629333334</v>
+        <v>-78.40347705333332</v>
       </c>
       <c r="P98">
-        <v>-309.6126651733333</v>
+        <v>-313.6139082133333</v>
       </c>
       <c r="Q98">
-        <v>-223.4126651733333</v>
+        <v>-227.4139082133333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.046401812408958</v>
+        <v>1.379935749878612</v>
       </c>
       <c r="T98">
-        <v>20.57342641478325</v>
+        <v>27.431235219711</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03879350008746839</v>
+        <v>0.03839356709687593</v>
       </c>
       <c r="W98">
-        <v>0.226652492679375</v>
+        <v>0.2267467968785567</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1939675004373419</v>
+        <v>0.1919678354843797</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2613424654685584</v>
+        <v>0.2632424654685583</v>
       </c>
       <c r="C99">
-        <v>-1534.535928761411</v>
+        <v>-1558.753052859317</v>
       </c>
       <c r="D99">
-        <v>344.031071238589</v>
+        <v>341.0249471406823</v>
       </c>
       <c r="E99">
-        <v>984.8669999999997</v>
+        <v>1006.078</v>
       </c>
       <c r="F99">
-        <v>2057.467</v>
+        <v>2078.678</v>
       </c>
       <c r="G99">
         <v>178.9</v>
@@ -9536,37 +9536,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M99">
-        <v>485.1507185999999</v>
+        <v>490.1522724</v>
       </c>
       <c r="N99">
-        <v>-392.0173852666666</v>
+        <v>-397.0189390666667</v>
       </c>
       <c r="O99">
-        <v>-78.40347705333332</v>
+        <v>-79.40378781333334</v>
       </c>
       <c r="P99">
-        <v>-313.6139082133333</v>
+        <v>-317.6151512533334</v>
       </c>
       <c r="Q99">
-        <v>-227.4139082133333</v>
+        <v>-231.4151512533334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.379935749878612</v>
+        <v>2.047003624817917</v>
       </c>
       <c r="T99">
-        <v>27.431235219711</v>
+        <v>41.1468528295665</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03839356709687593</v>
+        <v>0.03800179600405066</v>
       </c>
       <c r="W99">
-        <v>0.2267467968785567</v>
+        <v>0.2268391765022449</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1919678354843797</v>
+        <v>0.1900089800202532</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2632424654685583</v>
+        <v>0.2651424654685584</v>
       </c>
       <c r="C100">
-        <v>-1558.753052859317</v>
+        <v>-1582.918097340322</v>
       </c>
       <c r="D100">
-        <v>341.0249471406823</v>
+        <v>338.0709026596779</v>
       </c>
       <c r="E100">
-        <v>1006.078</v>
+        <v>1027.289</v>
       </c>
       <c r="F100">
-        <v>2078.678</v>
+        <v>2099.889</v>
       </c>
       <c r="G100">
         <v>178.9</v>
@@ -9618,37 +9618,37 @@
         <v>93.13333333333335</v>
       </c>
       <c r="M100">
-        <v>490.1522724</v>
+        <v>495.1538262</v>
       </c>
       <c r="N100">
-        <v>-397.0189390666667</v>
+        <v>-402.0204928666666</v>
       </c>
       <c r="O100">
-        <v>-79.40378781333334</v>
+        <v>-80.40409857333333</v>
       </c>
       <c r="P100">
-        <v>-317.6151512533334</v>
+        <v>-321.6163942933333</v>
       </c>
       <c r="Q100">
-        <v>-231.4151512533334</v>
+        <v>-235.4163942933333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.047003624817917</v>
+        <v>4.048207249635833</v>
       </c>
       <c r="T100">
-        <v>41.1468528295665</v>
+        <v>82.29370565913298</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03800179600405066</v>
+        <v>0.03761793947875722</v>
       </c>
       <c r="W100">
-        <v>0.2268391765022449</v>
+        <v>0.2269296898709091</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1900089800202532</v>
+        <v>0.1880896973937861</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2651424654685584</v>
-      </c>
-      <c r="C101">
-        <v>-1582.918097340322</v>
-      </c>
-      <c r="D101">
-        <v>338.0709026596779</v>
-      </c>
-      <c r="E101">
-        <v>1027.289</v>
-      </c>
-      <c r="F101">
-        <v>2099.889</v>
-      </c>
-      <c r="G101">
-        <v>178.9</v>
-      </c>
-      <c r="H101">
-        <v>1048.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>179.3333333333333</v>
-      </c>
-      <c r="K101">
-        <v>86.19999999999999</v>
-      </c>
-      <c r="L101">
-        <v>93.13333333333335</v>
-      </c>
-      <c r="M101">
-        <v>495.1538262</v>
-      </c>
-      <c r="N101">
-        <v>-402.0204928666666</v>
-      </c>
-      <c r="O101">
-        <v>-80.40409857333333</v>
-      </c>
-      <c r="P101">
-        <v>-321.6163942933333</v>
-      </c>
-      <c r="Q101">
-        <v>-235.4163942933333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.048207249635833</v>
-      </c>
-      <c r="T101">
-        <v>82.29370565913298</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03761793947875722</v>
-      </c>
-      <c r="W101">
-        <v>0.2269296898709091</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1880896973937861</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
